--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prajna\Documents\HORTIBONN\PROJECTS\Onion_DA_model\hotri_bonn_Repo\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8E9587-4EAB-41D0-862E-A81C6E25A3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400C0F09-134A-405D-BA45-D0717A427AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2325" windowWidth="38640" windowHeight="21120" tabRatio="815" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-2325" windowWidth="38640" windowHeight="21120" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="310">
   <si>
     <t>variable</t>
   </si>
@@ -592,18 +592,6 @@
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinanderfolgende Tage mit günstigen Bedingungen für Hagel das Risiko beeinflussen.</t>
   </si>
   <si>
-    <t>latitude_koeln_bonn_c</t>
-  </si>
-  <si>
-    <t>Latitude [°N]</t>
-  </si>
-  <si>
-    <t>Breitengrad von Köln Bonn (Referenzort)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zwiebelbauer;Zwiebel Anbauberater;Datenanalyst </t>
-  </si>
-  <si>
     <t>HI_onions_t</t>
   </si>
   <si>
@@ -628,15 +616,6 @@
     <t>Spagelbauer;Datenanalyst;Market analyst;Policy-maker</t>
   </si>
   <si>
-    <t>rain_window_days_sowing_p</t>
-  </si>
-  <si>
-    <t>Rainfall window before sowing [days]</t>
-  </si>
-  <si>
-    <t>The number of days before sowing is considered for the rainfall accumulation check.</t>
-  </si>
-  <si>
     <t>leaf_area_em_per_plant_p</t>
   </si>
   <si>
@@ -988,10 +967,10 @@
     <t>Bestimmt, wie leer das pflanzenverfügbare Bodenwasserreservoir sein darf, bevor eine Bewässerung ausgelöst wird. Ein Wert von 0,5 bedeutet: Sobald die Hälfte des nutzbaren Wassers verbraucht ist, wird bewässert.</t>
   </si>
   <si>
-    <t>Bodenparameter</t>
-  </si>
-  <si>
     <t>slider1</t>
+  </si>
+  <si>
+    <t>Bewässerungsparameter</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1447,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1574,10 +1553,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1609,10 +1588,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1644,10 +1623,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1">
@@ -1679,10 +1658,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1">
@@ -1714,15 +1693,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B7" s="15">
         <v>45</v>
@@ -1734,13 +1713,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -1749,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1784,12 +1763,12 @@
         <v>161</v>
       </c>
       <c r="K8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B9" s="15">
         <v>0.65</v>
@@ -1816,7 +1795,7 @@
         <v>161</v>
       </c>
       <c r="K9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1908,10 +1887,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1943,10 +1922,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1978,10 +1957,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2013,10 +1992,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2161,10 +2140,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2196,10 +2175,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2231,10 +2210,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2266,10 +2245,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2397,7 +2376,7 @@
         <v>76</v>
       </c>
       <c r="K3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2432,7 +2411,7 @@
         <v>76</v>
       </c>
       <c r="K4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -2450,7 +2429,7 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>87</v>
@@ -2465,7 +2444,7 @@
         <v>77</v>
       </c>
       <c r="K5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2483,10 +2462,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2498,7 +2477,7 @@
         <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2534,10 +2513,10 @@
         <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G9" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2549,7 +2528,7 @@
         <v>161</v>
       </c>
       <c r="K9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2569,10 +2548,10 @@
         <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="G10" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2584,7 +2563,7 @@
         <v>161</v>
       </c>
       <c r="K10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2602,7 +2581,7 @@
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G11" t="s">
         <v>182</v>
@@ -2617,12 +2596,12 @@
         <v>161</v>
       </c>
       <c r="K11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -2635,10 +2614,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G12" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2650,7 +2629,7 @@
         <v>161</v>
       </c>
       <c r="K12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2670,7 +2649,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B15" s="13">
         <v>30</v>
@@ -2685,10 +2664,10 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G15" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2697,10 +2676,10 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K15" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -2708,7 +2687,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B16" s="14">
         <v>0.6</v>
@@ -2721,10 +2700,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" s="12" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="G16" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -2733,10 +2712,10 @@
         <v>0.1</v>
       </c>
       <c r="J16" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K16" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -2744,7 +2723,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B17" s="14">
         <v>0.5</v>
@@ -2757,10 +2736,10 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="12" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G17" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2769,10 +2748,10 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -2780,7 +2759,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B18" s="14">
         <v>0.05</v>
@@ -2793,10 +2772,10 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G18" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2805,10 +2784,10 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -3006,7 +2985,7 @@
         <v>170</v>
       </c>
       <c r="G3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -3018,7 +2997,7 @@
         <v>161</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3041,7 +3020,7 @@
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -3053,7 +3032,7 @@
         <v>161</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3076,7 +3055,7 @@
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -3088,7 +3067,7 @@
         <v>161</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3109,7 +3088,7 @@
         <v>172</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -3121,7 +3100,7 @@
         <v>161</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3142,7 +3121,7 @@
         <v>100</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -3154,7 +3133,7 @@
         <v>161</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3175,7 +3154,7 @@
         <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -3187,7 +3166,7 @@
         <v>161</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3222,10 +3201,10 @@
         <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G11" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -3237,7 +3216,7 @@
         <v>161</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3257,10 +3236,10 @@
         <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="G12" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -3272,7 +3251,7 @@
         <v>161</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3292,10 +3271,10 @@
         <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G13" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -3307,7 +3286,7 @@
         <v>161</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3327,10 +3306,10 @@
         <v>78</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -3342,7 +3321,7 @@
         <v>161</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3360,10 +3339,10 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -3375,7 +3354,7 @@
         <v>161</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3393,10 +3372,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G16" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3408,7 +3387,7 @@
         <v>161</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3445,10 +3424,10 @@
         <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G19" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -3460,7 +3439,7 @@
         <v>161</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3480,10 +3459,10 @@
         <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G20" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -3495,7 +3474,7 @@
         <v>161</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3515,10 +3494,10 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G21" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -3530,7 +3509,7 @@
         <v>161</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3550,10 +3529,10 @@
         <v>78</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H22" t="s">
         <v>19</v>
@@ -3565,7 +3544,7 @@
         <v>161</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3583,10 +3562,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3598,7 +3577,7 @@
         <v>161</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3616,10 +3595,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="G24" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3631,7 +3610,7 @@
         <v>161</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3681,10 +3660,10 @@
         <v>78</v>
       </c>
       <c r="F27" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G27" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
@@ -3696,7 +3675,7 @@
         <v>161</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3716,10 +3695,10 @@
         <v>92</v>
       </c>
       <c r="F28" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G28" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
@@ -3731,7 +3710,7 @@
         <v>161</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3751,10 +3730,10 @@
         <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G29" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -3766,7 +3745,7 @@
         <v>161</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3784,10 +3763,10 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -3799,7 +3778,7 @@
         <v>161</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3817,10 +3796,10 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
@@ -3832,7 +3811,7 @@
         <v>161</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3850,10 +3829,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G32" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -3865,7 +3844,7 @@
         <v>161</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -4145,7 +4124,7 @@
         <v>119</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -4180,7 +4159,7 @@
         <v>119</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4215,7 +4194,7 @@
         <v>119</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4250,7 +4229,7 @@
         <v>119</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4285,12 +4264,12 @@
         <v>119</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B7" s="5">
         <v>50</v>
@@ -4302,13 +4281,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G7" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4317,15 +4296,15 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B8" s="5">
         <v>150</v>
@@ -4337,13 +4316,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G8" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4352,15 +4331,15 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B9" s="5">
         <v>300</v>
@@ -4372,13 +4351,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G9" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -4387,15 +4366,15 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B10" s="5">
         <v>200</v>
@@ -4407,13 +4386,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G10" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -4422,10 +4401,10 @@
         <v>0.1</v>
       </c>
       <c r="J10" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4449,7 +4428,7 @@
         <v>139</v>
       </c>
       <c r="H11" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="I11">
         <v>0.05</v>
@@ -4458,7 +4437,7 @@
         <v>76</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4493,7 +4472,7 @@
         <v>76</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4528,7 +4507,7 @@
         <v>76</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4563,7 +4542,7 @@
         <v>76</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4598,7 +4577,7 @@
         <v>76</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4633,7 +4612,7 @@
         <v>76</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4668,7 +4647,7 @@
         <v>76</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4703,7 +4682,7 @@
         <v>76</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4758,7 +4737,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B2">
         <v>0.13</v>
@@ -4770,13 +4749,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="F2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="G2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4785,15 +4764,15 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B3">
         <v>0.9</v>
@@ -4805,13 +4784,13 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="G3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -4820,15 +4799,15 @@
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B4">
         <v>0.9</v>
@@ -4840,30 +4819,30 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F4" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="G4" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="H4" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="I4">
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B5">
         <v>0.5</v>
@@ -4875,13 +4854,13 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -4890,15 +4869,15 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -4910,13 +4889,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="F6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G6" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -4925,15 +4904,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B7">
         <v>15</v>
@@ -4945,13 +4924,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F7" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="G7" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4960,15 +4939,15 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B8">
         <v>30</v>
@@ -4980,13 +4959,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F8" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G8" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4995,15 +4974,15 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B9">
         <v>40</v>
@@ -5015,13 +4994,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F9" t="s">
         <v>288</v>
       </c>
-      <c r="F9" t="s">
-        <v>295</v>
-      </c>
       <c r="G9" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -5030,15 +5009,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B10">
         <v>50</v>
@@ -5050,13 +5029,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F10" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G10" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -5065,15 +5044,15 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B11">
         <v>0.6</v>
@@ -5085,10 +5064,10 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G11" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -5100,12 +5079,12 @@
         <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B12">
         <v>1.3</v>
@@ -5117,10 +5096,10 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G12" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -5132,12 +5111,12 @@
         <v>76</v>
       </c>
       <c r="K12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B13">
         <v>1.4</v>
@@ -5149,10 +5128,10 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G13" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -5164,12 +5143,12 @@
         <v>76</v>
       </c>
       <c r="K13" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -5181,10 +5160,10 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G14" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -5196,7 +5175,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5285,82 +5264,37 @@
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3">
-        <v>50.866</v>
-      </c>
-      <c r="C3">
-        <v>50.866</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
       <c r="E3"/>
-      <c r="F3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>191</v>
-      </c>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>193</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>191</v>
-      </c>
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="4"/>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prajna\Documents\HORTIBONN\PROJECTS\Onion_DA_model\hotri_bonn_Repo\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400C0F09-134A-405D-BA45-D0717A427AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89814147-CD52-442C-89E0-0EE8D92D7742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2325" windowWidth="38640" windowHeight="21120" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="815" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="309">
   <si>
     <t>variable</t>
   </si>
@@ -607,24 +607,12 @@
     <t>Zwiebel</t>
   </si>
   <si>
-    <t>Spagelbauer</t>
-  </si>
-  <si>
-    <t>Spagelbauer;Zwiebelbauer;Zwiebel Anbauberater;Datenanalyst;Market analyst;Policy-maker</t>
-  </si>
-  <si>
-    <t>Spagelbauer;Datenanalyst;Market analyst;Policy-maker</t>
-  </si>
-  <si>
     <t>leaf_area_em_per_plant_p</t>
   </si>
   <si>
     <t>Blattfläche pro Pflanze Feldaufgang [cm²]</t>
   </si>
   <si>
-    <t>Zwiebel Anbauberater; Datenanalyst</t>
-  </si>
-  <si>
     <t>Blattfläche pro Pflanze vegetative Phase [cm²]</t>
   </si>
   <si>
@@ -655,9 +643,6 @@
     <t>Tag des Jahres, an dem die Aussaat der Zwiebeln im Modell erfolgt. Ein früherer oder späterer Saatstermin verschiebt den gesamten Vegetationsverlauf in die jeweils kühleren oder wärmeren Jahreszeiten und beeinflusst damit alle Stress- und Wachstumsprozesse.</t>
   </si>
   <si>
-    <t>Zwiebelanbauberater; Zwiebelbauer; Datenanalyst</t>
-  </si>
-  <si>
     <t>Maximale einseitige Blattfläche je Pflanze in der Keimungsphase. Dieser Wert wird mit der Pflanzdichte kombiniert, um den Blattflächenindex (LAI) für die jeweilige Phase zu berechnen und steuert damit, wie viel Strahlung die Kultur abfangen kann.</t>
   </si>
   <si>
@@ -971,6 +956,18 @@
   </si>
   <si>
     <t>Bewässerungsparameter</t>
+  </si>
+  <si>
+    <t>Spargelbauer</t>
+  </si>
+  <si>
+    <t>Spargelbauer;Datenanalyst;Marktanalyst;Politischer Entscheidungsträger</t>
+  </si>
+  <si>
+    <t>Zwiebel Anbauberater;Zwiebelbauer;Datenanalyst</t>
+  </si>
+  <si>
+    <t>Spargelbauer;Zwiebelbauer;Zwiebel Anbauberater;Datenanalyst;Marktanalyst;Politischer Entscheidungsträger</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1444,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1553,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="K2" t="s">
         <v>186</v>
@@ -1588,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="K3" t="s">
         <v>186</v>
@@ -1623,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="K4" t="s">
         <v>186</v>
@@ -1658,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
         <v>186</v>
@@ -1693,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K6" t="s">
         <v>186</v>
@@ -1701,7 +1698,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B7" s="15">
         <v>45</v>
@@ -1713,13 +1710,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -1728,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>204</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1887,7 +1884,7 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
         <v>186</v>
@@ -1922,7 +1919,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
         <v>186</v>
@@ -1957,7 +1954,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
         <v>186</v>
@@ -1992,7 +1989,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
         <v>186</v>
@@ -2140,7 +2137,7 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
         <v>186</v>
@@ -2175,7 +2172,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
         <v>186</v>
@@ -2210,7 +2207,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
         <v>186</v>
@@ -2245,7 +2242,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
         <v>186</v>
@@ -2429,7 +2426,7 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>87</v>
@@ -2462,10 +2459,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6" t="s">
         <v>243</v>
-      </c>
-      <c r="G6" t="s">
-        <v>248</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2513,10 +2510,10 @@
         <v>78</v>
       </c>
       <c r="F9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G9" t="s">
         <v>244</v>
-      </c>
-      <c r="G9" t="s">
-        <v>249</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2548,10 +2545,10 @@
         <v>92</v>
       </c>
       <c r="F10" t="s">
+        <v>240</v>
+      </c>
+      <c r="G10" t="s">
         <v>245</v>
-      </c>
-      <c r="G10" t="s">
-        <v>250</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2581,7 +2578,7 @@
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G11" t="s">
         <v>182</v>
@@ -2614,10 +2611,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G12" t="s">
         <v>246</v>
-      </c>
-      <c r="G12" t="s">
-        <v>251</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2649,7 +2646,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B15" s="13">
         <v>30</v>
@@ -2664,10 +2661,10 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G15" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2676,7 +2673,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K15" t="s">
         <v>187</v>
@@ -2687,7 +2684,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B16" s="14">
         <v>0.6</v>
@@ -2700,10 +2697,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" s="12" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G16" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -2712,7 +2709,7 @@
         <v>0.1</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K16" t="s">
         <v>187</v>
@@ -2723,7 +2720,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B17" s="14">
         <v>0.5</v>
@@ -2736,10 +2733,10 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="12" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2748,7 +2745,7 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K17" t="s">
         <v>187</v>
@@ -2759,7 +2756,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B18" s="14">
         <v>0.05</v>
@@ -2772,10 +2769,10 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G18" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2784,7 +2781,7 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K18" t="s">
         <v>187</v>
@@ -2985,7 +2982,7 @@
         <v>170</v>
       </c>
       <c r="G3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -3020,7 +3017,7 @@
         <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -3055,7 +3052,7 @@
         <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -3088,7 +3085,7 @@
         <v>172</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -3121,7 +3118,7 @@
         <v>100</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -3154,7 +3151,7 @@
         <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -3201,10 +3198,10 @@
         <v>78</v>
       </c>
       <c r="F11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G11" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -3236,10 +3233,10 @@
         <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -3271,10 +3268,10 @@
         <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G13" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -3306,10 +3303,10 @@
         <v>78</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -3339,10 +3336,10 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -3372,10 +3369,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G16" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3424,10 +3421,10 @@
         <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G19" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -3459,10 +3456,10 @@
         <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G20" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -3494,10 +3491,10 @@
         <v>92</v>
       </c>
       <c r="F21" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G21" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -3529,10 +3526,10 @@
         <v>78</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H22" t="s">
         <v>19</v>
@@ -3562,10 +3559,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3595,10 +3592,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G24" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3660,10 +3657,10 @@
         <v>78</v>
       </c>
       <c r="F27" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G27" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
@@ -3695,10 +3692,10 @@
         <v>92</v>
       </c>
       <c r="F28" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G28" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
@@ -3730,10 +3727,10 @@
         <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G29" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -3763,10 +3760,10 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -3796,10 +3793,10 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
@@ -3829,10 +3826,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G32" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -4269,7 +4266,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B7" s="5">
         <v>50</v>
@@ -4281,13 +4278,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4296,7 +4293,7 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>187</v>
@@ -4304,7 +4301,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B8" s="5">
         <v>150</v>
@@ -4316,13 +4313,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4331,7 +4328,7 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>187</v>
@@ -4339,7 +4336,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B9" s="5">
         <v>300</v>
@@ -4351,13 +4348,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -4366,7 +4363,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>187</v>
@@ -4374,7 +4371,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B10" s="5">
         <v>200</v>
@@ -4386,13 +4383,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -4401,7 +4398,7 @@
         <v>0.1</v>
       </c>
       <c r="J10" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>187</v>
@@ -4428,7 +4425,7 @@
         <v>139</v>
       </c>
       <c r="H11" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I11">
         <v>0.05</v>
@@ -4698,6 +4695,7 @@
   <cols>
     <col min="6" max="6" width="28.88671875" customWidth="1"/>
     <col min="7" max="7" width="37.44140625" customWidth="1"/>
+    <col min="10" max="10" width="42.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4737,7 +4735,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B2">
         <v>0.13</v>
@@ -4749,13 +4747,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4764,7 +4762,7 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K2" t="s">
         <v>187</v>
@@ -4772,7 +4770,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B3">
         <v>0.9</v>
@@ -4784,13 +4782,13 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -4799,7 +4797,7 @@
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K3" t="s">
         <v>187</v>
@@ -4807,7 +4805,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B4">
         <v>0.9</v>
@@ -4819,22 +4817,22 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G4" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I4">
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K4" t="s">
         <v>187</v>
@@ -4842,7 +4840,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B5">
         <v>0.5</v>
@@ -4854,13 +4852,13 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F5" t="s">
         <v>270</v>
       </c>
-      <c r="F5" t="s">
-        <v>275</v>
-      </c>
       <c r="G5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -4869,7 +4867,7 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K5" t="s">
         <v>187</v>
@@ -4877,7 +4875,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -4889,13 +4887,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F6" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -4904,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K6" t="s">
         <v>187</v>
@@ -4912,7 +4910,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B7">
         <v>15</v>
@@ -4924,13 +4922,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4939,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K7" t="s">
         <v>187</v>
@@ -4947,7 +4945,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B8">
         <v>30</v>
@@ -4959,13 +4957,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G8" t="s">
         <v>281</v>
-      </c>
-      <c r="F8" t="s">
-        <v>285</v>
-      </c>
-      <c r="G8" t="s">
-        <v>286</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4974,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K8" t="s">
         <v>187</v>
@@ -4982,7 +4980,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B9">
         <v>40</v>
@@ -4994,13 +4992,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F9" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -5009,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K9" t="s">
         <v>187</v>
@@ -5017,7 +5015,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B10">
         <v>50</v>
@@ -5029,13 +5027,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G10" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -5044,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="K10" t="s">
         <v>187</v>
@@ -5052,7 +5050,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B11">
         <v>0.6</v>
@@ -5064,10 +5062,10 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G11" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -5084,7 +5082,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B12">
         <v>1.3</v>
@@ -5096,10 +5094,10 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G12" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -5116,7 +5114,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B13">
         <v>1.4</v>
@@ -5128,10 +5126,10 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G13" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -5148,7 +5146,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -5160,10 +5158,10 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G14" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -5196,7 +5194,7 @@
     <col min="6" max="6" width="21" style="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="1" customWidth="1"/>
     <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="70.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="106.88671875" style="1" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -5264,7 +5262,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>189</v>
+        <v>308</v>
       </c>
       <c r="K2" t="s">
         <v>185</v>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prajna\Documents\HORTIBONN\PROJECTS\Onion_DA_model\hotri_bonn_Repo\Climate_Impact_on_Crop_Yield\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89814147-CD52-442C-89E0-0EE8D92D7742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E5A7B6-FBE7-4E63-B2C2-D96AE18BE742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="815" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="324">
   <si>
     <t>variable</t>
   </si>
@@ -274,9 +274,6 @@
     <t>Datenanalyst</t>
   </si>
   <si>
-    <t>Zwiebelbauer;Zwiebel Anbauberater</t>
-  </si>
-  <si>
     <t>mm/Tag</t>
   </si>
   <si>
@@ -289,21 +286,9 @@
     <t>prec_extreme_rain_medium_p</t>
   </si>
   <si>
-    <t>Niederschlagsschwelle Starkregen mittel</t>
-  </si>
-  <si>
-    <t>Tägliche Niederschlagsmenge, ab der ein mittleres Starkregenrisiko besteht.</t>
-  </si>
-  <si>
     <t>prec_extreme_rain_high_p</t>
   </si>
   <si>
-    <t>Niederschlagsschwelle Starkregen hoch</t>
-  </si>
-  <si>
-    <t>Tägliche Niederschlagsmenge, ab der ein hohes Starkregenrisiko besteht.</t>
-  </si>
-  <si>
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinanderfolgende Starkregentage das Risiko beeinflussen.</t>
   </si>
   <si>
@@ -349,18 +334,9 @@
     <t>Topt_botrytis_p</t>
   </si>
   <si>
-    <t>Optimumtemperatur Zwiebelhalsfäule</t>
-  </si>
-  <si>
-    <t>Toleranzwert um Optimum Zwiebelhalsfäule</t>
-  </si>
-  <si>
     <t>yield_reduction_botrytis_t</t>
   </si>
   <si>
-    <t>Ertragsminderung Zwiebelhalsfäule</t>
-  </si>
-  <si>
     <t>Falscher Mehltau (Peronospora destructor)</t>
   </si>
   <si>
@@ -400,60 +376,36 @@
     <t>yield_reduction_thrips_t</t>
   </si>
   <si>
-    <t>Zwiebel Anbauberater;Datenanalyst</t>
-  </si>
-  <si>
     <t>GDD_field_emergence_required_p</t>
   </si>
   <si>
     <t>°C Tage</t>
   </si>
   <si>
-    <t>Wachstumsgradtage/Wärmesumme Feldaufgang</t>
-  </si>
-  <si>
     <t>Benötigte Wärmesumme (in Wachstumsgradtagen) bis zum Ende der Feldaufgangsphase</t>
   </si>
   <si>
     <t>GDD_vegetative_required_p</t>
   </si>
   <si>
-    <t>Wachstumsgradtage/Wärmesumme vegetative Phase</t>
-  </si>
-  <si>
     <t>Benötigte Wärmesumme (in Wachstumsgradtagen) bis zum Ende der vegetativen Phase</t>
   </si>
   <si>
     <t>GDD_bulbing_required_p</t>
   </si>
   <si>
-    <t>Wachstumsgradtage/Wärmesumme Knollenbildungsphase</t>
-  </si>
-  <si>
     <t>Benötigte Wärmesumme (in Wachstumsgradtagen) bis zum Ende der Knollenbildungsphase</t>
   </si>
   <si>
     <t>GDD_maturation_required_p</t>
   </si>
   <si>
-    <t xml:space="preserve">Wachstumsgradtage/Wärmesumme Abreifephase </t>
-  </si>
-  <si>
     <t xml:space="preserve">Benötigte Wärmesumme (in Wachstumsgradtagen) bis zum Ende der Abreisephase </t>
   </si>
   <si>
-    <t>LUE_onion_p</t>
-  </si>
-  <si>
     <t>g/MJ</t>
   </si>
   <si>
-    <t>Lichtnutzungseffizienz Zwiebel</t>
-  </si>
-  <si>
-    <t>Biomasseproduktion pro Einheit eingestrahlter und genutzter Strahlung (g/MJ).</t>
-  </si>
-  <si>
     <t>lec_k_c</t>
   </si>
   <si>
@@ -466,84 +418,24 @@
     <t>f_T_1_upper_p</t>
   </si>
   <si>
-    <t>Temperatur obere Grenze f(T)=1</t>
-  </si>
-  <si>
-    <t>Obere Temperaturgrenze (°C), bis zu der Biomassewachstum optimal bleibt.</t>
-  </si>
-  <si>
     <t>f_T_1_lower_p</t>
   </si>
   <si>
-    <t>Temperatur untere Grenze f(T)=1</t>
-  </si>
-  <si>
-    <t>Untere Temperaturgrenze (°C), ab der Biomassewachstum optimal bleibt.</t>
-  </si>
-  <si>
     <t>f_T_0_upper_p</t>
   </si>
   <si>
-    <t>Temperatur obere Grenze f(T)=0</t>
-  </si>
-  <si>
-    <t>Temperatur (°C), oberhalb derer kein Biomassewachstum mehr stattfindet.</t>
-  </si>
-  <si>
     <t>f_T_0_lower_p</t>
   </si>
   <si>
-    <t>Temperatur untere Grenze f(T)=0</t>
-  </si>
-  <si>
-    <t>Temperatur (°C), unterhalb derer kein Biomassewachstum mehr stattfindet.</t>
-  </si>
-  <si>
-    <t>f_W_1_upper_p</t>
-  </si>
-  <si>
-    <t>Niederschlag obere Grenze f(W)=1</t>
-  </si>
-  <si>
-    <t>Täglicher Niederschlag (mm/Tag), bis zu dem Wasser nicht limitierend wirkt.</t>
-  </si>
-  <si>
-    <t>f_W_1_lower_p</t>
-  </si>
-  <si>
-    <t>Niederschlag untere Grenze f(W)=1</t>
-  </si>
-  <si>
-    <t>Täglicher Niederschlag (mm/Tag), ab dem Wasser nicht limitierend wirkt.</t>
-  </si>
-  <si>
-    <t>f_W_0.5_p</t>
-  </si>
-  <si>
-    <t>Niederschlag f(W)=0.5</t>
-  </si>
-  <si>
-    <t>Täglicher Niederschlag (mm/Tag), bei dem das Biomassewachstum auf 50 % reduziert ist.</t>
-  </si>
-  <si>
-    <t>Zwiebelbauer;Zwiebel Anbauberater;Datenanalyst</t>
-  </si>
-  <si>
     <t>Ernte Index</t>
   </si>
   <si>
-    <t>Anteil der geernteten Speicherorgane (Zwiebelknollen) an der gesamten oberirdischen Biomasse der Pflanze</t>
-  </si>
-  <si>
     <t>onions_per_ha_p</t>
   </si>
   <si>
     <t>Pflanzen/ha</t>
   </si>
   <si>
-    <t xml:space="preserve">Zwiebeldichte </t>
-  </si>
-  <si>
     <t xml:space="preserve">Aussaatmenge an Zwiebeln pro Hektar </t>
   </si>
   <si>
@@ -553,9 +445,6 @@
     <t>rh_botrytis_threshold_p</t>
   </si>
   <si>
-    <t>Schwellenwert  tägliche durchschnittliche Relative Luftfeuchtigkeit Zwiebelhalsfäule</t>
-  </si>
-  <si>
     <t>impact_rh_botrytis_t</t>
   </si>
   <si>
@@ -619,15 +508,9 @@
     <t>leaf_area_bl_per_plant_p</t>
   </si>
   <si>
-    <t>Blattfläche pro Pflanze Knollenbildungsphase [cm²]</t>
-  </si>
-  <si>
     <t>leaf_area_mt_per_plant_p</t>
   </si>
   <si>
-    <t>Blattfläche pro Pflanze Abreifephase [cm²]</t>
-  </si>
-  <si>
     <t>leaf_area_veg_per_plant_p</t>
   </si>
   <si>
@@ -655,9 +538,6 @@
     <t>Maximale einseitige Blattfläche je Pflanze in der Reifephase. Dieser Wert wird mit der Pflanzdichte kombiniert, um den Blattflächenindex (LAI) für die jeweilige Phase zu berechnen und steuert damit, wie viel Strahlung die Kultur abfangen kann.</t>
   </si>
   <si>
-    <t>Relative Luftfeuchte, ab der günstige Bedingungen für Botrytis im Bestand angenommen werden. Längere Phasen hoher Luftfeuchte erhöhen das Risiko von Blatt- und Bulbeninfektionen.</t>
-  </si>
-  <si>
     <t>Temperatur, bei der das Risiko für Botrytisinfektionen im Modell am höchsten ist. In diesem Bereich verlaufen Infektion und Krankheitssymptome besonders schnell.</t>
   </si>
   <si>
@@ -670,51 +550,6 @@
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinanderfolgende feuchte Tage das Risiko beeinflussen.</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei einem Botrytis-Ereignis verloren geht (0.5 = 50% Abnahme des Biomassezuwachs). Der Parameter steht für die Ertragswirkung von Blatt- und Halsfälen (Botrytis spp.), die die Blattgesundheit, Assimilationsleistung und Lagerfähigkeit der Zwiebeln beeinträchtigen. Im Modell führt ein ausgelöstes Botrytis-Ereignis in einer Phase dazu, dass der dort mögliche Biomassezuwachs um diesen Anteil reduziert wird.</t>
-  </si>
-  <si>
-    <t>Luftfeuchteschwelle Falscher Mehltau</t>
-  </si>
-  <si>
-    <t>Temperaturoptimum Falscher Mehltau</t>
-  </si>
-  <si>
-    <t>Temperaturbereich Falscher Mehltau</t>
-  </si>
-  <si>
-    <t>Wirkungsfaktor Relative Luftfeuchte</t>
-  </si>
-  <si>
-    <t>Ertragsverlust durch Falschen Mehltau</t>
-  </si>
-  <si>
-    <t>Luftfeuchteschwelle Fusarium</t>
-  </si>
-  <si>
-    <t>Bodentemperaturoptimum Fusarium</t>
-  </si>
-  <si>
-    <t>Temperaturbereich Fusarium (Boden)</t>
-  </si>
-  <si>
-    <t>Ertragsverlust durch Fusarium</t>
-  </si>
-  <si>
-    <t>Luftfeuchteschwelle für Thripse</t>
-  </si>
-  <si>
-    <t>Temperaturoptimum Thripse</t>
-  </si>
-  <si>
-    <t>Temperaturbereich Thripse</t>
-  </si>
-  <si>
-    <t>Wirkungsfaktor aufeinanderfolgende Trockentage</t>
-  </si>
-  <si>
-    <t>Ertragsverlust durch Thripse</t>
-  </si>
-  <si>
     <t>Relative Luftfeuchte, ab der günstige Bedingungen für Falschen Mehltau angenommen werden. Hohe Luftfeuchte begünstigt Sporulation und Infektion der Blätter.</t>
   </si>
   <si>
@@ -724,9 +559,6 @@
     <t>Breite des Temperaturfensters, in dem Falscher Mehltau aktiv sein kann. Ein größerer Wert lässt Infektionen in einem breiteren Temperaturspektrum zu.</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei Auftreten von Falschem Mehltau (Peronospora destructor) verloren geht (0.5 = 50% Abnahme des Biomassezuwachs). Der Parameter beschreibt den Verlust an grünem Blattapparat und Photosyntheseleistung, der durch Mehltaubefall verursacht wird. Wenn das klimatische Risiko in einer Phase hoch genug ist und das Modell ein Mehltau-Ereignis auslöst, wird der theoretische Biomassezuwachs dieser Phase um den angegebenen Anteil reduziert.</t>
-  </si>
-  <si>
     <t>Relative Luftfeuchte, ab der Bedingungen für Fusariuminfektionen begünstigt werden. Hohe Luftfeuchte in Kombination mit geeigneten Bodentemperaturen erhöht das Risiko von Wurzel- und Bulbenfäulen.</t>
   </si>
   <si>
@@ -736,9 +568,6 @@
     <t>Breite des Bodentemperaturbereichs, in dem Fusarium im Modell als aktiv betrachtet wird. Ein größerer Wert bedeutet eine höhere Aktivität über ein breiteres Temperaturspektrum im Boden.</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei einem Fusarium-Befall verloren geht (0.5 = 50% Abnahme des Biomassezuwachs). Der Parameter beschreibt die Stärke des Schadens durch Fusarium-Infektionen (z.B. Wurzel- und Zwiebelbasalfäulen), die Wasser- und Nährstoffaufnahme sowie die Vitalität des Bestandes mindern. Bei Eintreten eines Fusarium-Ereignisses in einer Phase wird der phasenweise Biomassezuwachs um diesen Anteil reduziert.</t>
-  </si>
-  <si>
     <t>Relative Luftfeuchte, unterhalb derer günstige Bedingungen für Thripse angenommen werden. Trockene Luft begünstigt in der Regel Thripse und erhöht das Risiko von Saugschäden am Laub.</t>
   </si>
   <si>
@@ -754,45 +583,21 @@
     <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei einem relevanten Thripsbefall verloren geht (0.5 = 50% Abnahme des Biomassezuwachs). Der Parameter quantifiziert den durch Saugschäden verursachten Rückgang der funktionsfähigen Blattfläche (Silberungen, Nekrosen) und damit der Biomasseproduktion. Wird im Modell für eine Phase ein Thrips-Stressereignis ausgelöst, reduziert dieser Parameter den phasenweisen Biomassezuwachs um den angegebenen Anteil.</t>
   </si>
   <si>
-    <t xml:space="preserve">Wirkungsfaktor aufeinanderfolgende Starkregentage </t>
-  </si>
-  <si>
-    <t>Ertragsverlust bei Starkregen</t>
-  </si>
-  <si>
-    <t>Niederschlagsschwelle für Hagelereignisse</t>
-  </si>
-  <si>
-    <t>Temperaturschwelle für Hagelereignisse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ertragsverlust bei Hagelereignis </t>
-  </si>
-  <si>
     <t>Wirkungsfaktor Tage  mit Hagelbedingungen</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei einem extremen Niederschlagsereignis (Starkregen/Staunässe) verloren geht. Der Parameter beschreibt, wie stark sich Schäden durch Verschlämmung, Sauerstoffmangel im Wurzelraum oder Lager verursachende Niederschläge auf das Biomassewachstum auswirken (0.5 = Abnahme Biomassezuwachs um 50%). Tritt ein vom Modell identifiziertes Extremniederschlagsereignis in einer Phase ein, wird der phasenweise Biomassezuwachs um diesen Anteil reduziert.</t>
-  </si>
-  <si>
     <t>Tägliche Niederschlagsmenge, ab der zusammen mit geeigneten Temperaturbedingungen ein Hagelereignis im Modell angenommen wird. Höhere Schwellenwerte führen zu weniger, aber intensiveren modellierten Hagelereignissen.</t>
   </si>
   <si>
     <t>Mittlere Tagestemperatur, in deren Bereich zusammen mit ausreichendem Niederschlag Hagel angenommen wird. Dieser Parameter grenzt den Zeitraum der Saison ein, in dem Hagel im Modell auftreten kann.</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der beim Eintritt eines Hagelereignisses verloren geht. Der Parameter spiegelt die durch Hagel verursachten direkten Schäden an Blattoberfläche und Spross wider, die die photosynthetisch aktive Fläche und damit das Biomassewachstum reduzieren (0.5 = Abnahme Biomassezuwachs um 50%). Wenn das Modell für eine Phase ein Hagelereignis auslöst, wird der entsprechende Biomassezuwachs um diesen Anteil gekürzt.</t>
-  </si>
-  <si>
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark Temperaur das Hitzestress Risiko beeinflussen.</t>
   </si>
   <si>
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinander folgende Hitzetage das Hitzestress Risiko beeinflussen.</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei einem Hitzestress-Ereignis verloren geht (0.5 = Abnahme um des Biomassezuwachs um 50%). Der Parameter quantifiziert die Schwere des Schadens, den die Kultur durch Hitzestress erfährt. Ein höherer Wert bedeutet, dass ein aufgetretener Hitzestress einen größeren Anteil des phasenweisen Biomassezuwachses reduziert (multiplikativer Reduktionsfaktor).</t>
-  </si>
-  <si>
     <t>Tmax_heat_threshold_p</t>
   </si>
   <si>
@@ -811,15 +616,6 @@
     <t>yield_reduction_heat_t</t>
   </si>
   <si>
-    <t>Ertragsverlust bei Hitzestress</t>
-  </si>
-  <si>
-    <t>Temperaturschwelle für Hitzestress</t>
-  </si>
-  <si>
-    <t>Tageslufttemperatur, ab der im Modell Hitzestress für Zwiebeln angenommen wird. Werden höhere Temperaturen über mehrere Tage erreicht, sinkt die Photosyntheseleistung und die Biomassebildung wird reduziert.</t>
-  </si>
-  <si>
     <t>cm²</t>
   </si>
   <si>
@@ -829,81 +625,42 @@
     <t>mm cm⁻¹</t>
   </si>
   <si>
-    <t>Pflanzenverfügbare Nutzbare Feldkapazität pro cm Wurzeltiefe. Bestimmt TAW</t>
-  </si>
-  <si>
-    <t>Dieser Parameter gibt an, wie viele Millimeter Wasser pro Zentimeter Wurzelzone vom Boden für die Pflanze verfügbar sind – also wie viel Wasser der Boden speichern kann, das die Zwiebel auch wirklich aufnehmen kann.</t>
-  </si>
-  <si>
-    <t>fc_init_frac_c</t>
-  </si>
-  <si>
     <t>Anteil (0–1)</t>
   </si>
   <si>
-    <t>Feldkapazitätsanteil zu Vegetationsbeginn</t>
-  </si>
-  <si>
-    <t>fc_target_frac_c</t>
-  </si>
-  <si>
-    <t>Ziel-Feldkapazitätsanteil nach Bewässerung</t>
-  </si>
-  <si>
     <t>deplete_trigger_fr_t</t>
   </si>
   <si>
-    <t>Schwellenwert für Bewässerungsauslösung (RAW)</t>
-  </si>
-  <si>
     <t>max_irrig_mm_p</t>
   </si>
   <si>
     <t>mm Ereignis⁻¹</t>
   </si>
   <si>
-    <t>maximale Bewässerungsgabe pro Ereignis</t>
-  </si>
-  <si>
-    <t>Maximale Wassermenge pro Bewässerungsmaßnahme, die im Modell aufgebracht werden kann. Dieser Wert spiegelt technische und bodenphysikalische Grenzen wider (Infiltration, Staunässe).</t>
-  </si>
-  <si>
     <t>root_em_cm_p</t>
   </si>
   <si>
     <t>cm</t>
   </si>
   <si>
-    <t>effektive Wurzeltiefe (Keimungsphase)</t>
-  </si>
-  <si>
     <t>Effektive mittlere Wurzeltiefe der Zwiebel in der Keimungsphase. Sie bestimmt zusammen mit der nutzbaren Feldkapazität, wie viel Wasser die Pflanzen aus dem Bodenprofil aufnehmen können.</t>
   </si>
   <si>
     <t>root_vg_cm_p</t>
   </si>
   <si>
-    <t>effektive Wurzeltiefe (vegetative Phase)</t>
-  </si>
-  <si>
     <t>Effektive mittlere Wurzeltiefe der Zwiebel in der vegetative Phase. Sie bestimmt zusammen mit der nutzbaren Feldkapazität, wie viel Wasser die Pflanzen aus dem Bodenprofil aufnehmen können.</t>
   </si>
   <si>
     <t>root_bl_cm_p</t>
   </si>
   <si>
-    <t>effektive Wurzeltiefe (Bulbing-Phase)</t>
-  </si>
-  <si>
     <t>Effektive mittlere Wurzeltiefe der Zwiebel in der Bulbing-Phase. Sie bestimmt zusammen mit der nutzbaren Feldkapazität, wie viel Wasser die Pflanzen aus dem Bodenprofil aufnehmen können.</t>
   </si>
   <si>
     <t>root_mt_cm_p</t>
   </si>
   <si>
-    <t>effektive Wurzeltiefe (Reifephase)</t>
-  </si>
-  <si>
     <t>Effektive mittlere Wurzeltiefe der Zwiebel in der Reifephase. Sie bestimmt zusammen mit der nutzbaren Feldkapazität, wie viel Wasser die Pflanzen aus dem Bodenprofil aufnehmen können.</t>
   </si>
   <si>
@@ -943,31 +700,319 @@
     <t>Crop-Koeffizient (Kc) der Zwiebel in der Reifephase. Der Kc-Wert skaliert die Referenzverdunstung (ET₀) zur kulturartspezifischen Evapotranspiration (ETc).</t>
   </si>
   <si>
-    <t>Beschreibt, wie voll das pflanzenverfügbare Bodenwasserreservoir zu Saisonbeginn ist. Ein Wert von 0,9 bedeutet, dass der Boden beim Start fast vollständig mit nutzbarem Wasser gefüllt ist.</t>
-  </si>
-  <si>
-    <t>Gibt an, bis zu welchem Füllstand des pflanzenverfügbaren Bodenwassers eine Bewässerung den Boden wieder auffüllen soll. Ein Wert von 0,8 bedeutet, dass nach einer Bewässerung rund 80 % des nutzbaren Wasserpuffers erreicht werden sollen.</t>
-  </si>
-  <si>
-    <t>Bestimmt, wie leer das pflanzenverfügbare Bodenwasserreservoir sein darf, bevor eine Bewässerung ausgelöst wird. Ein Wert von 0,5 bedeutet: Sobald die Hälfte des nutzbaren Wassers verbraucht ist, wird bewässert.</t>
-  </si>
-  <si>
     <t>slider1</t>
   </si>
   <si>
     <t>Bewässerungsparameter</t>
   </si>
   <si>
-    <t>Spargelbauer</t>
-  </si>
-  <si>
-    <t>Spargelbauer;Datenanalyst;Marktanalyst;Politischer Entscheidungsträger</t>
-  </si>
-  <si>
-    <t>Zwiebel Anbauberater;Zwiebelbauer;Datenanalyst</t>
-  </si>
-  <si>
-    <t>Spargelbauer;Zwiebelbauer;Zwiebel Anbauberater;Datenanalyst;Marktanalyst;Politischer Entscheidungsträger</t>
+    <t>Zwiebeldichte [Zwiebeln/ha]</t>
+  </si>
+  <si>
+    <t>Temperaturbereich für Hagelereignisse [°C]</t>
+  </si>
+  <si>
+    <t>Maximale Tageslufttemperatur, ab der im Modell Hitzestress für Zwiebeln angenommen wird. Werden höhere Temperaturen über mehrere Tage erreicht, sinkt die Photosyntheseleistung und die Biomassebildung wird reduziert.</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Ab dieser Regenmenge pro Tag besteht mittleres Risiko für Schäden durch zu hohe Niederschläge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wirkungsfaktor aufeinanderfolgender potentieller Starkregentage </t>
+  </si>
+  <si>
+    <t>Wie viel Prozent des Wachstums geht bei einem Hitzestress-Ereignis in der jeweiligen Wachstumsphase verloren? (z.B. 0.1 = 10% weniger Wachstum)</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent des Wachstums geht bei einem Hagelereignis in der jeweiligen Wachstumsphase verloren? (z.B. 0.5 = 50% weniger Wachstum durch Blatt- und Sprossschäden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wie viel Prozent des Wachstums geht bei einem Starkregenereignis in der jeweiligen Wachstumsphase verloren? (z.B. 0.5 = 50% weniger Wachstum durch Staunässe, Verschlämmung oder Lagerbildung)</t>
+  </si>
+  <si>
+    <t>Ab dieser relativen Luftfeuchtigkeit steigt das Risiko für Botrytis-Infektionen. Je länger hohe Luftfeuchtigkeit anhält, desto höher das Risiko für Blatt- und Zwiebelinfektionen.</t>
+  </si>
+  <si>
+    <t>Optimale Temperatur für Zwiebelhalsfäule [°C]</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent des Wachstums geht bei einem Botrytis-Befall in der jeweiligen Wachstumsphase verloren? (z.B. 0.5 = 50% weniger Wachstum durch Blatt- und Halsfäule, schlechtere Lagerfähigkeit</t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch Zwiebelhalsfäule</t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch durch Starkregen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wachstumsverlust durchdurch Hagelereignis </t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch Hitzestress</t>
+  </si>
+  <si>
+    <t>Optimale Temperatur für Falschen Mehltau [°C]</t>
+  </si>
+  <si>
+    <t>Temperaturbereich Falscher Mehltau [°C]</t>
+  </si>
+  <si>
+    <t>Wirkungsfaktor Relative Luftfeuchte Falscher Mehltau</t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch Falschen Mehltau</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent des Wachstums geht bei Mehltaubefall verloren? (z.B. 0.5 = 50% weniger Wachstum durch Blattverlust und reduzierte Photosynthese)</t>
+  </si>
+  <si>
+    <t>Optimale Bodentemperatur für Fusarium [°C]</t>
+  </si>
+  <si>
+    <t>Temperaturbereich  Zwiebelhalsfäule [°C]</t>
+  </si>
+  <si>
+    <t>Bodentemperaturbereich Fusarium [°C]</t>
+  </si>
+  <si>
+    <t>Wirkungsfaktor aufeinanderfolgende Regentage Falscher Mehltau</t>
+  </si>
+  <si>
+    <t>Wirkungsfaktor aufeinanderfolgende Regentage Fusarium</t>
+  </si>
+  <si>
+    <t>Wirkungsfaktor Relative Luftfeuchte Fusarium</t>
+  </si>
+  <si>
+    <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinanderfolgende Regentage das Risiko beeinflussen.</t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch Fusarium</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent des Wachstums geht bei Fusarium-Befall verloren? (z.B. 0.5 = 50% weniger Wachstum durch Wurzel- und Zwiebelfäule, schlechtere Wasser- und Nährstoffaufnahme)</t>
+  </si>
+  <si>
+    <t>Luftfeuchteschwelle Thripse (Überschreitung = Risiko) [%]</t>
+  </si>
+  <si>
+    <t>Luftfeuchteschwelle für Fusarium (Überschreitung = Risiko) [%]</t>
+  </si>
+  <si>
+    <t>Luftfeuchteschwelle für Falschen Mehltau (Überschreitung = Risiko)  [%]</t>
+  </si>
+  <si>
+    <t>Luftfeuchteschwelle für Zwiebelhalsfäule (Überschreitung = Risiko)  [%]</t>
+  </si>
+  <si>
+    <t>Ab dieser Regenmenge pro Tag besteht hohes Risiko für Schäden durch zu hohe Niederschläge</t>
+  </si>
+  <si>
+    <t>Tagesschwelle  Starkregen (mittleres Risiko) (Überschreitung = Risiko) [mm/Tag]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tagesschwelle Starkregen (hohes Risiko)(Überschreitung = Risiko) [mm/Tag]</t>
+  </si>
+  <si>
+    <t>Niederschlagsschwelle für Hagelereignisse (Überschreitung = Risiko) [mm/Tag]</t>
+  </si>
+  <si>
+    <t>Temperaturschwelle für Hitzestress (Überschreitung = Risiko) [°C]</t>
+  </si>
+  <si>
+    <t>Optimale Temperatur für Thripse [°C]</t>
+  </si>
+  <si>
+    <t>Temperaturtoleranz Thripse [°C]</t>
+  </si>
+  <si>
+    <t>Wirkungsfaktor Relative Luftfeuchte Thripse</t>
+  </si>
+  <si>
+    <t>Wirkungsfaktor aufeinanderfolgende Trockentage Thripse</t>
+  </si>
+  <si>
+    <t>Beschreibung: Wie viel Prozent des Wachstums geht bei Thripsbefall verloren? (z.B. 0.5 = 50% weniger Wachstum durch Saugschäden, Versilberungen und Nekrosen am Laub)</t>
+  </si>
+  <si>
+    <t>Wärmesumme bis Feldaufgang [°C-Tage]</t>
+  </si>
+  <si>
+    <t>Wärmesumme bis Ende vegetative Phase [°C-Tage]</t>
+  </si>
+  <si>
+    <t>Wärmesumme bis Ende Bulbenbildung [°C-Tage]</t>
+  </si>
+  <si>
+    <t>Wärmesumme bis Abreife [°C-Tage]</t>
+  </si>
+  <si>
+    <t>Wie viel Gramm Biomasse produziert die Pflanze pro Megajoule genutzter Sonnenstrahlung? Höhere Werte = effizientere Umwandlung von Licht in Wachstum.</t>
+  </si>
+  <si>
+    <t>Optimaler Wachstumsbereich Zwiebel: Obergrenze [°C]</t>
+  </si>
+  <si>
+    <t>Bis zu dieser Temperatur wächst die Zwiebel optimal. Darüber wird das Wachstum zunehmend gehemmt.</t>
+  </si>
+  <si>
+    <t>Optimaler Wachstumsbereich Zwiebel: Untergrenze [°C]</t>
+  </si>
+  <si>
+    <t>Ab dieser Temperatur wächst die Zwiebel optimal. Darunter wird das Wachstum zunehmend gehemmt.</t>
+  </si>
+  <si>
+    <t>dry_matter_content_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trockenmasseanteil </t>
+  </si>
+  <si>
+    <t>Anteil der Zwiebelknollen-Trockenmasse an der gesamten oberirdischen Pflanzen-Trockenmasse. Ein Wert von 0.75 bedeutet, dass 75% der produzierten Biomasse in die Zwiebelbulbe eingelagert werden und 25% in den restlichen Organen verbleiben.</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent der frischen Zwiebel ist Trockenmasse? (0.10 = 10% feste Substanz, Rest ist Wasser)</t>
+  </si>
+  <si>
+    <t>LUE_em_p</t>
+  </si>
+  <si>
+    <t>LUE_vg_p</t>
+  </si>
+  <si>
+    <t>LUE_bl_p</t>
+  </si>
+  <si>
+    <t>LUE_mt_p</t>
+  </si>
+  <si>
+    <t>Lichtnutzungseffizienz Feldaufgang [g/MJ]</t>
+  </si>
+  <si>
+    <t>Lichtnutzungseffizienz vegetative Phase [g/MJ]</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze Bulbenbildungsphase [cm²]</t>
+  </si>
+  <si>
+    <t>Lichtnutzungseffizienz Bulbenbildungsphase [g/MJ]</t>
+  </si>
+  <si>
+    <t>Lichtnutzungseffizienz Reifephase [g/MJ]</t>
+  </si>
+  <si>
+    <t>Blattfläche pro Pflanze Reifephase [cm²]</t>
+  </si>
+  <si>
+    <t>slider3</t>
+  </si>
+  <si>
+    <t>slider4</t>
+  </si>
+  <si>
+    <t>slider5</t>
+  </si>
+  <si>
+    <t>theta_rel (0-1</t>
+  </si>
+  <si>
+    <t>theta_rel (0-2</t>
+  </si>
+  <si>
+    <t>theta_rel (0-3</t>
+  </si>
+  <si>
+    <t>Optimaler Wasserbereich Zwiebel: Obergrenze [θ]</t>
+  </si>
+  <si>
+    <t>Optimaler Wasserbereich Zwiebel: Untergrenze [θ]</t>
+  </si>
+  <si>
+    <t>Wassermangel-Schwelle Zwiebel: 50% Wachstum [θ]</t>
+  </si>
+  <si>
+    <t>f_W_1_upper_t</t>
+  </si>
+  <si>
+    <t>f_W_1_lower_t</t>
+  </si>
+  <si>
+    <t>Temperatur ab der Wachstum auf 20%  reduziert ist.</t>
+  </si>
+  <si>
+    <t>Wachstumsreduktion Zwiebel auf 20%: Untergrenze [°C]</t>
+  </si>
+  <si>
+    <t>Wachstumsreduktion Zwiebel auf 20%: Obergrenze [°C]</t>
+  </si>
+  <si>
+    <t>Temperatur unter der Wachstum auf 20%  reduziert ist.</t>
+  </si>
+  <si>
+    <t>Oberhalb dieser Schwelle hat die Pflanze genug Wasser für maximales Wachstum (nahe Feldkapazität). θ beschreibt den Bodenwassergehalt: Bei θ = 1,0 ist der Boden optimal feucht (Feldkapazität), bei θ = 0,5 ist die Hälfte des nutzbaren Wassers verbraucht und bei θ = 0,0 ist der Welkepunkt erreicht. Zwiebeln reagieren wegen ihrer flachen Wurzeln sehr empfindlich und brauchen θ ≥ 0,7–0,8 für gutes Wachstum.</t>
+  </si>
+  <si>
+    <t>Bei diesem Bodenwassergehalt halbiert sich das Wachstum. Starker Wassermangel! Bei θ = 1,0 ist der Boden optimal feucht (Feldkapazität), bei θ = 0,5 ist die Hälfte des nutzbaren Wassers verbraucht und bei θ = 0,0 ist der Welkepunkt erreicht. Zwiebeln reagieren wegen ihrer flachen Wurzeln sehr empfindlich und brauchen θ ≥ 0,7–0,8 für gutes Wachstum.</t>
+  </si>
+  <si>
+    <t>Unterhalb dieser Schwelle beginnt Wasserstress. Zwiebeln brauchen viel Wasser wegen flacher Wurzeln. Bei θ = 1,0 ist der Boden optimal feucht (Feldkapazität), bei θ = 0,5 ist die Hälfte des nutzbaren Wassers verbraucht und bei θ = 0,0 ist der Welkepunkt erreicht. Zwiebeln reagieren wegen ihrer flachen Wurzeln sehr empfindlich und brauchen θ ≥ 0,7–0,8 für gutes Wachstum.</t>
+  </si>
+  <si>
+    <t>Pflanzenverfügbare Nutzbare Feldkapazität pro cm Wurzeltiefe [mm/cm</t>
+  </si>
+  <si>
+    <t>Gibt an wie viel pflanzenverfügbares Wasser pro Zentimeter Wurzeltiefe im Boden gespeichert werden kann. Dieser Wert multipliziert mit der Wurzeltiefe ergibt die Gesamtwasserspeicherkapazität (TAW). Höhere Werte = mehr Wasserpuffer für die Zwiebel.</t>
+  </si>
+  <si>
+    <t>Bodenwasservorrat zu Saisonbeginn [Anteil 0–1]</t>
+  </si>
+  <si>
+    <t>Bodenwasservorrat nach Bewässerung [Anteil 0–1]</t>
+  </si>
+  <si>
+    <t>Bewässerungsschwelle  [Anteil 0–1]</t>
+  </si>
+  <si>
+    <t>Maximale Bewässerungsmenge pro Gabe [mm]</t>
+  </si>
+  <si>
+    <t>effektive Wurzeltiefe (Keimungsphase) [cm]</t>
+  </si>
+  <si>
+    <t>effektive Wurzeltiefe (vegetative Phase) [cm]</t>
+  </si>
+  <si>
+    <t>effektive Wurzeltiefe (Bulbing-Phase) [cm]</t>
+  </si>
+  <si>
+    <t>effektive Wurzeltiefe (Reifephase) [cm]</t>
+  </si>
+  <si>
+    <t>Bestimmt bis zu welchem Füllstand eine Bewässerung den Bodenwasserspeicher wieder auffüllt. 0.8 = 80% bedeutet nach jeder Bewässerung wird der Boden auf 80% seiner nutzbaren Kapazität aufgefüllt. Höhere Werte = seltenere aber größere Bewässerungsgaben.</t>
+  </si>
+  <si>
+    <t>Definiert wann eine Bewässerung ausgelöst wird. Bei 0.5 wird bewässert sobald 50% des nutzbaren Bodenwassers verbraucht sind. Niedrigere Werte = frühere und häufigere Bewässerung mit weniger Trockenstress aber höherem Wasserverbrauch.</t>
+  </si>
+  <si>
+    <t>Begrenzt die Wassermenge die bei einer einzelnen Bewässerung aufgebracht werden kann. Wird durch Infiltrationskapazität des Bodens und Technik bestimmt. Höhere Werte können zu Oberflächenabfluss oder Staunässe führen.</t>
+  </si>
+  <si>
+    <t>Legt fest wie voll das Bodenwasserreservoir bei Vegetationsbeginn ist. 0.9 = 90% gefüllt bedeutet der Boden startet mit ausreichend Wasser. Beeinflusst ob zu Saisonbeginn bereits Bewässerung nötig ist</t>
+  </si>
+  <si>
+    <t>Landwirt;Anbauberater;Datenanalyst</t>
+  </si>
+  <si>
+    <t>f_W_0_5_t</t>
+  </si>
+  <si>
+    <t>fc_init_frac_t</t>
+  </si>
+  <si>
+    <t>fc_target_frac_t</t>
   </si>
 </sst>
 </file>
@@ -977,7 +1022,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1023,6 +1068,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF030712"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1045,7 +1097,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1080,9 +1132,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 3" xfId="1" xr:uid="{B655CD4E-4D88-4FFB-8DB5-A2F77832E90B}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1378,12 +1434,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19247B9C-F4A5-4DCC-BF21-E18D3CC8C8F5}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="73.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="49" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1428,15 +1484,15 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1444,7 +1500,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>304</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1476,14 +1532,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92018703-4177-49D8-B09E-62560F009CDF}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.109375" customWidth="1"/>
-    <col min="2" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.88671875" customWidth="1"/>
-    <col min="10" max="10" width="70.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="2" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.85546875" customWidth="1"/>
+    <col min="10" max="10" width="70.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1550,10 +1606,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K2" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1585,10 +1641,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K3" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1620,10 +1676,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K4" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1">
@@ -1655,10 +1711,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K5" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1">
@@ -1690,15 +1746,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K6" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="B7" s="15">
         <v>45</v>
@@ -1710,13 +1766,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="G7" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -1725,12 +1781,15 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>307</v>
+        <v>320</v>
+      </c>
+      <c r="K7" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="B8" s="15">
         <v>700000</v>
@@ -1742,13 +1801,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>166</v>
+        <v>221</v>
       </c>
       <c r="G8" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -1757,18 +1816,18 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K8" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="B9" s="15">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="C9" s="15">
         <v>0.85</v>
@@ -1777,10 +1836,10 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
-        <v>163</v>
+        <v>276</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -1789,10 +1848,42 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K9" t="s">
-        <v>187</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="15">
+        <v>0.09</v>
+      </c>
+      <c r="C10" s="15">
+        <v>0.11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <v>0.01</v>
+      </c>
+      <c r="J10" t="s">
+        <v>320</v>
+      </c>
+      <c r="K10" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1804,20 +1895,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{546B24F0-A477-4B95-8562-CC4F97744405}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="79" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="53.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="53.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1884,10 +1975,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K2" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1919,10 +2010,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K3" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1954,10 +2045,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K4" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1989,10 +2080,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K5" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2034,7 +2125,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" ht="15.6">
+    <row r="20" spans="1:7" ht="15.75">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2043,7 +2134,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="5"/>
     </row>
-    <row r="21" spans="1:7" ht="15.6">
+    <row r="21" spans="1:7" ht="15.75">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2061,16 +2152,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95267B7B-4544-45E1-AE00-31F080BD66E3}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="16.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="70.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="9" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="70.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2137,10 +2228,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K2" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2172,10 +2263,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K3" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2207,10 +2298,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K4" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2242,10 +2333,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K5" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2260,7 +2351,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2269,7 +2360,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2286,15 +2377,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49756CD-7B89-4299-B487-83FA9AC75873}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="60.109375" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="51.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="85.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="40.33203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="60.140625" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="51.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="85.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="40.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2334,7 +2425,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>75</v>
@@ -2343,7 +2434,7 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3">
         <v>25</v>
@@ -2355,13 +2446,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G3" t="s">
+        <v>225</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -2370,15 +2461,15 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K3" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -2390,13 +2481,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>85</v>
+        <v>257</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>86</v>
+        <v>255</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2405,15 +2496,15 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K4" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="B5">
         <v>0.3</v>
@@ -2426,10 +2517,10 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -2438,31 +2529,31 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="K5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B6">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C6">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G6" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2471,22 +2562,22 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="K6" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="H7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
     </row>
     <row r="8" spans="1:14">
       <c r="F8" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s">
         <v>75</v>
@@ -2495,7 +2586,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -2507,13 +2598,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="G9" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2522,15 +2613,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K9" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -2542,13 +2633,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2557,15 +2648,15 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K10" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B11">
         <v>0.3</v>
@@ -2578,10 +2669,10 @@
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -2590,31 +2681,31 @@
         <v>0.1</v>
       </c>
       <c r="J11" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K11" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="B12">
         <v>0.5</v>
       </c>
       <c r="C12">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G12" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2623,21 +2714,21 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K12" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="H13" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14">
       <c r="F14" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
         <v>75</v>
@@ -2646,7 +2737,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="B15" s="13">
         <v>30</v>
@@ -2658,13 +2749,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G15" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2673,10 +2764,10 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K15" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -2684,7 +2775,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="B16" s="14">
         <v>0.6</v>
@@ -2697,10 +2788,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" s="12" t="s">
-        <v>252</v>
+        <v>187</v>
       </c>
       <c r="G16" t="s">
-        <v>247</v>
+        <v>183</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -2709,10 +2800,10 @@
         <v>0.1</v>
       </c>
       <c r="J16" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K16" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -2720,7 +2811,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B17" s="14">
         <v>0.5</v>
@@ -2733,10 +2824,10 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="12" t="s">
-        <v>254</v>
+        <v>189</v>
       </c>
       <c r="G17" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2745,10 +2836,10 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K17" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -2756,7 +2847,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>255</v>
+        <v>190</v>
       </c>
       <c r="B18" s="14">
         <v>0.05</v>
@@ -2769,10 +2860,10 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="G18" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2781,10 +2872,10 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K18" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -2906,15 +2997,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8485F19-4118-CA49-B5A5-49D6574876CF}">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="60.109375" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="51.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="85.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="69.88671875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="60.140625" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="51.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="85.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="69.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customFormat="1">
@@ -2956,7 +3047,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>75</v>
@@ -2964,7 +3055,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="B3">
         <v>85</v>
@@ -2976,13 +3067,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="G3" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -2991,15 +3082,15 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -3011,13 +3102,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>231</v>
       </c>
       <c r="G4" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -3026,15 +3117,15 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3046,13 +3137,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="G5" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -3061,15 +3152,15 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="B6">
         <v>0.4</v>
@@ -3082,10 +3173,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -3094,15 +3185,15 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -3115,10 +3206,10 @@
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -3127,31 +3218,31 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B8">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="G8" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -3160,21 +3251,21 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="H9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:11">
       <c r="F10" s="10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
         <v>75</v>
@@ -3183,25 +3274,25 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="B11">
         <v>85</v>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="G11" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -3210,15 +3301,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -3230,13 +3321,13 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="G12" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -3245,15 +3336,15 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -3265,13 +3356,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="G13" t="s">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -3280,15 +3371,15 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -3300,13 +3391,13 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -3315,15 +3406,15 @@
         <v>0.1</v>
       </c>
       <c r="J14" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B15">
         <v>0.3</v>
@@ -3336,10 +3427,10 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -3348,31 +3439,31 @@
         <v>0.1</v>
       </c>
       <c r="J15" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B16">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C16">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="G16" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3381,22 +3472,22 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="G17"/>
       <c r="H17" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J17"/>
     </row>
     <row r="18" spans="1:11">
       <c r="F18" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G18"/>
       <c r="H18" t="s">
@@ -3406,25 +3497,25 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="G19" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -3433,15 +3524,15 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -3453,13 +3544,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="G20" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -3468,15 +3559,15 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -3488,13 +3579,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="G21" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -3503,15 +3594,15 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="B22">
         <v>0.1</v>
@@ -3523,13 +3614,13 @@
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="H22" t="s">
         <v>19</v>
@@ -3538,15 +3629,15 @@
         <v>0.1</v>
       </c>
       <c r="J22" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B23">
         <v>0.4</v>
@@ -3559,10 +3650,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3571,15 +3662,15 @@
         <v>0.1</v>
       </c>
       <c r="J23" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B24">
         <v>0.7</v>
@@ -3592,10 +3683,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="G24" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3604,10 +3695,10 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3619,7 +3710,7 @@
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -3631,7 +3722,7 @@
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" s="11" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G26"/>
       <c r="H26" t="s">
@@ -3642,25 +3733,25 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>78</v>
+        <v>224</v>
       </c>
       <c r="F27" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="G27" t="s">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
@@ -3669,15 +3760,15 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B28">
         <v>26</v>
@@ -3689,13 +3780,13 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="G28" t="s">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
@@ -3704,15 +3795,15 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -3724,13 +3815,13 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="G29" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -3739,15 +3830,15 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="B30">
         <v>0.3</v>
@@ -3760,10 +3851,10 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -3772,15 +3863,15 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B31">
         <v>0.2</v>
@@ -3793,10 +3884,10 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
@@ -3805,15 +3896,15 @@
         <v>0.1</v>
       </c>
       <c r="J31" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B32">
         <v>0.8</v>
@@ -3826,10 +3917,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="G32" t="s">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -3838,10 +3929,10 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -4042,16 +4133,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E27EF3F-1977-4DFD-AB2B-D5DA3F473BBD}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.109375" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="45.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="66.33203125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="40.88671875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="30.140625" style="1" customWidth="1"/>
+    <col min="2" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="45.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="66.28515625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="40.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customFormat="1">
@@ -4091,10 +4182,10 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C2">
         <v>300</v>
@@ -4103,13 +4194,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>122</v>
+        <v>265</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4118,18 +4209,18 @@
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="C3">
         <v>1100</v>
@@ -4138,13 +4229,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="G3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -4153,15 +4244,15 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B4">
         <v>1400</v>
@@ -4173,13 +4264,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>128</v>
+        <v>267</v>
       </c>
       <c r="G4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -4188,15 +4279,15 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B5">
         <v>1800</v>
@@ -4208,13 +4299,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="G5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -4223,33 +4314,33 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6">
-        <v>1.5</v>
-      </c>
-      <c r="C6">
-        <v>2.8</v>
+        <v>151</v>
+      </c>
+      <c r="B6" s="5">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5">
+        <v>40</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>136</v>
+        <v>152</v>
+      </c>
+      <c r="G6" t="s">
+        <v>161</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -4258,33 +4349,33 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="B7" s="5">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C7" s="5">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="G7" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4293,33 +4384,33 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="B8" s="5">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="C8" s="5">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>190</v>
+        <v>284</v>
       </c>
       <c r="G8" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4328,33 +4419,33 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="B9" s="5">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="C9" s="5">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="G9" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -4363,101 +4454,101 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="5">
-        <v>200</v>
-      </c>
-      <c r="C10" s="5">
-        <v>400</v>
+        <v>121</v>
+      </c>
+      <c r="B10">
+        <v>0.75</v>
+      </c>
+      <c r="C10">
+        <v>0.75</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>259</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E10"/>
       <c r="F10" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="G10" t="s">
-        <v>203</v>
+        <v>122</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="I10">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J10" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B11">
-        <v>0.65</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>0.65</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11"/>
-      <c r="F11" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>139</v>
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" t="s">
+        <v>270</v>
+      </c>
+      <c r="G11" t="s">
+        <v>271</v>
       </c>
       <c r="H11" t="s">
-        <v>303</v>
+        <v>19</v>
       </c>
       <c r="I11">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>142</v>
+        <v>87</v>
+      </c>
+      <c r="F12" t="s">
+        <v>272</v>
+      </c>
+      <c r="G12" t="s">
+        <v>273</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -4466,33 +4557,33 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>145</v>
+        <v>87</v>
+      </c>
+      <c r="F13" t="s">
+        <v>301</v>
+      </c>
+      <c r="G13" t="s">
+        <v>299</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -4501,33 +4592,33 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>148</v>
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G14" t="s">
+        <v>302</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -4536,33 +4627,33 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>297</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0.99</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>151</v>
+        <v>291</v>
+      </c>
+      <c r="F15" t="s">
+        <v>294</v>
+      </c>
+      <c r="G15" t="s">
+        <v>303</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -4574,30 +4665,30 @@
         <v>76</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>298</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>0.65</v>
       </c>
       <c r="D16" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>154</v>
+        <v>292</v>
+      </c>
+      <c r="F16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G16" t="s">
+        <v>305</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -4609,65 +4700,65 @@
         <v>76</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>155</v>
+        <v>321</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>0.35</v>
       </c>
       <c r="D17" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>157</v>
+        <v>293</v>
+      </c>
+      <c r="F17" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" t="s">
+        <v>304</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="s">
         <v>76</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>278</v>
       </c>
       <c r="B18">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C18">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>160</v>
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G18" t="s">
+        <v>269</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -4679,8 +4770,120 @@
         <v>76</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>187</v>
-      </c>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1.5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" t="s">
+        <v>269</v>
+      </c>
+      <c r="H19" t="s">
+        <v>288</v>
+      </c>
+      <c r="I19">
+        <v>0.1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20">
+        <v>4.5</v>
+      </c>
+      <c r="C20">
+        <v>5.5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" t="s">
+        <v>285</v>
+      </c>
+      <c r="G20" t="s">
+        <v>269</v>
+      </c>
+      <c r="H20" t="s">
+        <v>289</v>
+      </c>
+      <c r="I20">
+        <v>0.1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21">
+        <v>3.5</v>
+      </c>
+      <c r="C21">
+        <v>4.5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" t="s">
+        <v>286</v>
+      </c>
+      <c r="G21" t="s">
+        <v>269</v>
+      </c>
+      <c r="H21" t="s">
+        <v>290</v>
+      </c>
+      <c r="I21">
+        <v>0.1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4691,11 +4894,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4154656F-FDF7-4376-B538-AF0744710608}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="28.88671875" customWidth="1"/>
-    <col min="7" max="7" width="37.44140625" customWidth="1"/>
-    <col min="10" max="10" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" customWidth="1"/>
+    <col min="10" max="10" width="42.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4735,25 +4938,25 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="B2">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="C2">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>261</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G2" t="s">
-        <v>263</v>
+        <v>306</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>307</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4762,33 +4965,33 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K2" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>264</v>
+        <v>322</v>
       </c>
       <c r="B3">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G3" t="s">
-        <v>300</v>
+        <v>194</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -4797,68 +5000,68 @@
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K3" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="B4">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="C4">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F4" t="s">
-        <v>268</v>
-      </c>
-      <c r="G4" t="s">
-        <v>301</v>
+        <v>194</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>316</v>
       </c>
       <c r="H4" t="s">
-        <v>303</v>
+        <v>219</v>
       </c>
       <c r="I4">
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K4" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>195</v>
       </c>
       <c r="B5">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="F5" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" t="s">
-        <v>302</v>
+        <v>310</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>317</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -4867,15 +5070,15 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>196</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -4887,13 +5090,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>197</v>
       </c>
       <c r="F6" t="s">
-        <v>273</v>
-      </c>
-      <c r="G6" t="s">
-        <v>274</v>
+        <v>311</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>318</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -4902,33 +5105,33 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K6" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>198</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="F7" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="G7" t="s">
-        <v>278</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4937,33 +5140,33 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K7" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>201</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="F8" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="G8" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4972,33 +5175,33 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K8" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="G9" t="s">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -5007,33 +5210,33 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K9" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="B10">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C10">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="F10" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="G10" t="s">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -5042,30 +5245,30 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c r="K10" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="B11">
         <v>0.6</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="G11" t="s">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -5077,27 +5280,27 @@
         <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="B12">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="C12">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -5109,27 +5312,27 @@
         <v>76</v>
       </c>
       <c r="K12" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="B13">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>1.6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="G13" t="s">
-        <v>296</v>
+        <v>215</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -5141,27 +5344,27 @@
         <v>76</v>
       </c>
       <c r="K13" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>216</v>
       </c>
       <c r="B14">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="C14">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>298</v>
+        <v>217</v>
       </c>
       <c r="G14" t="s">
-        <v>299</v>
+        <v>218</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -5173,29 +5376,31 @@
         <v>76</v>
       </c>
       <c r="K14" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E46615A-8238-4E62-BD61-353FBA21321A}">
   <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="34.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="1"/>
     <col min="6" max="6" width="21" style="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="10" width="106.88671875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="9" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="106.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -5262,10 +5467,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="K2" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="L2"/>
       <c r="M2"/>
@@ -5303,7 +5508,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="15.6">
+    <row r="14" spans="1:14" ht="15.75">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5312,7 +5517,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:14" ht="15.6">
+    <row r="15" spans="1:14" ht="15.75">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5321,7 +5526,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:14" ht="15.6">
+    <row r="16" spans="1:14" ht="15.75">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -5330,7 +5535,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" ht="15.6">
+    <row r="17" spans="1:7" ht="15.75">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -5339,7 +5544,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.6">
+    <row r="18" spans="1:7" ht="15.75">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -5348,7 +5553,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.6">
+    <row r="19" spans="1:7" ht="15.75">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\GitHub\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E5A7B6-FBE7-4E63-B2C2-D96AE18BE742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1882757-E841-446E-8A53-89B442B59E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11385" tabRatio="815" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="325">
   <si>
     <t>variable</t>
   </si>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>fc_target_frac_t</t>
+  </si>
+  <si>
+    <t>silder2</t>
   </si>
 </sst>
 </file>
@@ -4209,7 +4212,7 @@
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>76</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>150</v>
@@ -4244,7 +4247,7 @@
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>76</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>150</v>
@@ -4279,7 +4282,7 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>76</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>150</v>
@@ -4314,7 +4317,7 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>76</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>150</v>
@@ -4662,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>150</v>
@@ -4697,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>150</v>
@@ -4732,7 +4735,7 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>320</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>150</v>
@@ -4994,7 +4997,7 @@
         <v>319</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>324</v>
       </c>
       <c r="I3">
         <v>0.05</v>
@@ -5029,7 +5032,7 @@
         <v>316</v>
       </c>
       <c r="H4" t="s">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="I4">
         <v>0.05</v>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\GitHub\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1882757-E841-446E-8A53-89B442B59E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CCA279-560F-45BE-A2C7-2ACEBAA57429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11385" tabRatio="815" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -580,9 +580,6 @@
     <t>Gewichtungsfaktor (0–1), der angibt, wie stark aufeinanderfolgende trockene Tage das Risiko beeinflussen.</t>
   </si>
   <si>
-    <t>Anteil des potenziellen Biomassezuwachses in der jeweiligen Wachstumsphase, der bei einem relevanten Thripsbefall verloren geht (0.5 = 50% Abnahme des Biomassezuwachs). Der Parameter quantifiziert den durch Saugschäden verursachten Rückgang der funktionsfähigen Blattfläche (Silberungen, Nekrosen) und damit der Biomasseproduktion. Wird im Modell für eine Phase ein Thrips-Stressereignis ausgelöst, reduziert dieser Parameter den phasenweisen Biomassezuwachs um den angegebenen Anteil.</t>
-  </si>
-  <si>
     <t>Wirkungsfaktor Tage  mit Hagelbedingungen</t>
   </si>
   <si>
@@ -835,9 +832,6 @@
     <t>Wirkungsfaktor aufeinanderfolgende Trockentage Thripse</t>
   </si>
   <si>
-    <t>Beschreibung: Wie viel Prozent des Wachstums geht bei Thripsbefall verloren? (z.B. 0.5 = 50% weniger Wachstum durch Saugschäden, Versilberungen und Nekrosen am Laub)</t>
-  </si>
-  <si>
     <t>Wärmesumme bis Feldaufgang [°C-Tage]</t>
   </si>
   <si>
@@ -1016,6 +1010,12 @@
   </si>
   <si>
     <t>silder2</t>
+  </si>
+  <si>
+    <t>Wie viel Prozent des Wachstums geht bei Thripsbefall verloren? (z.B. 0.5 = 50% weniger Wachstum durch Saugschäden, Versilberungen und Nekrosen am Laub)</t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch Thripse</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1539,7 +1539,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="66.85546875" customWidth="1"/>
     <col min="10" max="10" width="70.140625" bestFit="1" customWidth="1"/>
@@ -1609,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K2" t="s">
         <v>149</v>
@@ -1644,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K3" t="s">
         <v>149</v>
@@ -1679,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K4" t="s">
         <v>149</v>
@@ -1714,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K5" t="s">
         <v>149</v>
@@ -1749,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K6" t="s">
         <v>149</v>
@@ -1784,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K7" t="s">
         <v>150</v>
@@ -1795,10 +1796,10 @@
         <v>129</v>
       </c>
       <c r="B8" s="15">
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="C8" s="15">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
@@ -1807,7 +1808,7 @@
         <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G8" t="s">
         <v>131</v>
@@ -1819,7 +1820,7 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K8" t="s">
         <v>150</v>
@@ -1830,10 +1831,10 @@
         <v>146</v>
       </c>
       <c r="B9" s="15">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="C9" s="15">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
@@ -1842,7 +1843,7 @@
         <v>128</v>
       </c>
       <c r="G9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -1851,7 +1852,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K9" t="s">
         <v>150</v>
@@ -1859,7 +1860,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B10" s="15">
         <v>0.09</v>
@@ -1871,10 +1872,10 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>275</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>277</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -1883,7 +1884,7 @@
         <v>0.01</v>
       </c>
       <c r="J10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K10" t="s">
         <v>150</v>
@@ -1978,7 +1979,7 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K2" t="s">
         <v>149</v>
@@ -2013,7 +2014,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K3" t="s">
         <v>149</v>
@@ -2048,7 +2049,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K4" t="s">
         <v>149</v>
@@ -2083,7 +2084,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K5" t="s">
         <v>149</v>
@@ -2231,7 +2232,7 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K2" t="s">
         <v>149</v>
@@ -2266,7 +2267,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K3" t="s">
         <v>149</v>
@@ -2301,7 +2302,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K4" t="s">
         <v>149</v>
@@ -2336,7 +2337,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K5" t="s">
         <v>149</v>
@@ -2452,10 +2453,10 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -2464,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K3" t="s">
         <v>150</v>
@@ -2487,10 +2488,10 @@
         <v>77</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2499,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K4" t="s">
         <v>150</v>
@@ -2520,7 +2521,7 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>82</v>
@@ -2532,7 +2533,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K5" t="s">
         <v>150</v>
@@ -2553,10 +2554,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2565,7 +2566,7 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K6" t="s">
         <v>150</v>
@@ -2604,10 +2605,10 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2616,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K9" t="s">
         <v>150</v>
@@ -2639,10 +2640,10 @@
         <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2651,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K10" t="s">
         <v>150</v>
@@ -2662,7 +2663,7 @@
         <v>88</v>
       </c>
       <c r="B11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C11">
         <v>0.8</v>
@@ -2672,7 +2673,7 @@
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" t="s">
         <v>145</v>
@@ -2684,7 +2685,7 @@
         <v>0.1</v>
       </c>
       <c r="J11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K11" t="s">
         <v>150</v>
@@ -2705,10 +2706,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2717,7 +2718,7 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K12" t="s">
         <v>150</v>
@@ -2740,7 +2741,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" s="13">
         <v>30</v>
@@ -2755,10 +2756,10 @@
         <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2767,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K15" t="s">
         <v>150</v>
@@ -2778,7 +2779,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="14">
         <v>0.6</v>
@@ -2791,10 +2792,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -2803,7 +2804,7 @@
         <v>0.1</v>
       </c>
       <c r="J16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K16" t="s">
         <v>150</v>
@@ -2814,7 +2815,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="14">
         <v>0.5</v>
@@ -2827,10 +2828,10 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2839,7 +2840,7 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K17" t="s">
         <v>150</v>
@@ -2850,7 +2851,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" s="14">
         <v>0.05</v>
@@ -2863,10 +2864,10 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2875,7 +2876,7 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K18" t="s">
         <v>150</v>
@@ -3073,10 +3074,10 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -3085,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>150</v>
@@ -3108,7 +3109,7 @@
         <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G4" t="s">
         <v>165</v>
@@ -3120,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>150</v>
@@ -3143,7 +3144,7 @@
         <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G5" t="s">
         <v>166</v>
@@ -3155,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>150</v>
@@ -3188,7 +3189,7 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>150</v>
@@ -3221,7 +3222,7 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>150</v>
@@ -3242,10 +3243,10 @@
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -3254,7 +3255,7 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>150</v>
@@ -3292,7 +3293,7 @@
         <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G11" t="s">
         <v>169</v>
@@ -3304,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>150</v>
@@ -3327,7 +3328,7 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G12" t="s">
         <v>170</v>
@@ -3339,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>150</v>
@@ -3362,7 +3363,7 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G13" t="s">
         <v>171</v>
@@ -3374,7 +3375,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>150</v>
@@ -3397,7 +3398,7 @@
         <v>77</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>167</v>
@@ -3409,7 +3410,7 @@
         <v>0.1</v>
       </c>
       <c r="J14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>150</v>
@@ -3430,7 +3431,7 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>167</v>
@@ -3442,7 +3443,7 @@
         <v>0.1</v>
       </c>
       <c r="J15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>150</v>
@@ -3463,10 +3464,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
+        <v>239</v>
+      </c>
+      <c r="G16" t="s">
         <v>240</v>
-      </c>
-      <c r="G16" t="s">
-        <v>241</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3475,7 +3476,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>150</v>
@@ -3515,7 +3516,7 @@
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G19" t="s">
         <v>172</v>
@@ -3527,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>150</v>
@@ -3550,7 +3551,7 @@
         <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G20" t="s">
         <v>173</v>
@@ -3562,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>150</v>
@@ -3585,7 +3586,7 @@
         <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
         <v>174</v>
@@ -3597,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>150</v>
@@ -3620,7 +3621,7 @@
         <v>77</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>167</v>
@@ -3632,7 +3633,7 @@
         <v>0.1</v>
       </c>
       <c r="J22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>150</v>
@@ -3653,10 +3654,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3665,7 +3666,7 @@
         <v>0.1</v>
       </c>
       <c r="J23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>150</v>
@@ -3686,10 +3687,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
+        <v>248</v>
+      </c>
+      <c r="G24" t="s">
         <v>249</v>
-      </c>
-      <c r="G24" t="s">
-        <v>250</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3698,7 +3699,7 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>150</v>
@@ -3748,10 +3749,10 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G27" t="s">
         <v>175</v>
@@ -3763,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>150</v>
@@ -3786,7 +3787,7 @@
         <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G28" t="s">
         <v>176</v>
@@ -3798,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>150</v>
@@ -3821,7 +3822,7 @@
         <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G29" t="s">
         <v>177</v>
@@ -3833,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>150</v>
@@ -3854,7 +3855,7 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>167</v>
@@ -3866,7 +3867,7 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>150</v>
@@ -3887,7 +3888,7 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>178</v>
@@ -3899,7 +3900,7 @@
         <v>0.1</v>
       </c>
       <c r="J31" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>150</v>
@@ -3920,10 +3921,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="G32" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -3932,7 +3933,7 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>150</v>
@@ -4200,7 +4201,7 @@
         <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G2" t="s">
         <v>113</v>
@@ -4235,7 +4236,7 @@
         <v>112</v>
       </c>
       <c r="F3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G3" t="s">
         <v>115</v>
@@ -4270,7 +4271,7 @@
         <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G4" t="s">
         <v>117</v>
@@ -4305,7 +4306,7 @@
         <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G5" t="s">
         <v>119</v>
@@ -4337,7 +4338,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>152</v>
@@ -4352,7 +4353,7 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>150</v>
@@ -4372,7 +4373,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>153</v>
@@ -4387,7 +4388,7 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>150</v>
@@ -4407,10 +4408,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G8" t="s">
         <v>163</v>
@@ -4422,7 +4423,7 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>150</v>
@@ -4442,10 +4443,10 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G9" t="s">
         <v>164</v>
@@ -4457,7 +4458,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>150</v>
@@ -4484,7 +4485,7 @@
         <v>123</v>
       </c>
       <c r="H10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I10">
         <v>0.05</v>
@@ -4513,10 +4514,10 @@
         <v>87</v>
       </c>
       <c r="F11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -4525,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>150</v>
@@ -4548,10 +4549,10 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -4560,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>150</v>
@@ -4583,10 +4584,10 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -4595,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>150</v>
@@ -4618,10 +4619,10 @@
         <v>87</v>
       </c>
       <c r="F14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" t="s">
         <v>300</v>
-      </c>
-      <c r="G14" t="s">
-        <v>302</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -4630,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>150</v>
@@ -4638,7 +4639,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B15">
         <v>0.9</v>
@@ -4650,13 +4651,13 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G15" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -4665,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>150</v>
@@ -4673,7 +4674,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B16">
         <v>0.55000000000000004</v>
@@ -4685,13 +4686,13 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G16" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -4700,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>150</v>
@@ -4708,7 +4709,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B17">
         <v>0.25</v>
@@ -4720,13 +4721,13 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -4735,7 +4736,7 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>150</v>
@@ -4743,7 +4744,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B18">
         <v>0.6</v>
@@ -4758,10 +4759,10 @@
         <v>120</v>
       </c>
       <c r="F18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -4778,7 +4779,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4793,13 +4794,13 @@
         <v>120</v>
       </c>
       <c r="F19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H19" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I19">
         <v>0.1</v>
@@ -4813,7 +4814,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B20">
         <v>4.5</v>
@@ -4828,13 +4829,13 @@
         <v>120</v>
       </c>
       <c r="F20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I20">
         <v>0.1</v>
@@ -4848,7 +4849,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B21">
         <v>3.5</v>
@@ -4863,13 +4864,13 @@
         <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I21">
         <v>0.1</v>
@@ -4941,7 +4942,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2">
         <v>0.16</v>
@@ -4953,13 +4954,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4968,7 +4969,7 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K2" t="s">
         <v>150</v>
@@ -4976,7 +4977,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B3">
         <v>0.85</v>
@@ -4988,22 +4989,22 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I3">
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K3" t="s">
         <v>150</v>
@@ -5011,7 +5012,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B4">
         <v>0.85</v>
@@ -5023,13 +5024,13 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -5038,7 +5039,7 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K4" t="s">
         <v>150</v>
@@ -5046,7 +5047,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5">
         <v>0.25</v>
@@ -5058,13 +5059,13 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -5073,7 +5074,7 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K5" t="s">
         <v>150</v>
@@ -5081,7 +5082,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -5093,13 +5094,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -5108,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K6" t="s">
         <v>150</v>
@@ -5116,7 +5117,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B7">
         <v>12</v>
@@ -5128,13 +5129,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" t="s">
         <v>199</v>
-      </c>
-      <c r="F7" t="s">
-        <v>312</v>
-      </c>
-      <c r="G7" t="s">
-        <v>200</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -5143,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K7" t="s">
         <v>150</v>
@@ -5151,7 +5152,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -5163,13 +5164,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -5178,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K8" t="s">
         <v>150</v>
@@ -5186,7 +5187,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B9">
         <v>22</v>
@@ -5198,13 +5199,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -5213,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K9" t="s">
         <v>150</v>
@@ -5221,7 +5222,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B10">
         <v>27</v>
@@ -5233,13 +5234,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -5248,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K10" t="s">
         <v>150</v>
@@ -5256,7 +5257,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B11">
         <v>0.6</v>
@@ -5268,10 +5269,10 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" t="s">
         <v>208</v>
-      </c>
-      <c r="G11" t="s">
-        <v>209</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -5288,7 +5289,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B12">
         <v>0.9</v>
@@ -5300,10 +5301,10 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" t="s">
         <v>211</v>
-      </c>
-      <c r="G12" t="s">
-        <v>212</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -5320,7 +5321,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -5332,10 +5333,10 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
+        <v>213</v>
+      </c>
+      <c r="G13" t="s">
         <v>214</v>
-      </c>
-      <c r="G13" t="s">
-        <v>215</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -5352,7 +5353,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B14">
         <v>0.75</v>
@@ -5364,10 +5365,10 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" t="s">
         <v>217</v>
-      </c>
-      <c r="G14" t="s">
-        <v>218</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -5470,7 +5471,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K2" t="s">
         <v>148</v>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\GitHub\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CCA279-560F-45BE-A2C7-2ACEBAA57429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0845C9F0-5B71-4C75-8C0F-8EC213108C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="321">
   <si>
     <t>variable</t>
   </si>
@@ -310,9 +310,6 @@
     <t>impact_days_hail_t</t>
   </si>
   <si>
-    <t>Trockenstress</t>
-  </si>
-  <si>
     <t>Biotische Schäden</t>
   </si>
   <si>
@@ -697,9 +694,6 @@
     <t>Crop-Koeffizient (Kc) der Zwiebel in der Reifephase. Der Kc-Wert skaliert die Referenzverdunstung (ET₀) zur kulturartspezifischen Evapotranspiration (ETc).</t>
   </si>
   <si>
-    <t>slider1</t>
-  </si>
-  <si>
     <t>Bewässerungsparameter</t>
   </si>
   <si>
@@ -901,15 +895,6 @@
     <t>Blattfläche pro Pflanze Reifephase [cm²]</t>
   </si>
   <si>
-    <t>slider3</t>
-  </si>
-  <si>
-    <t>slider4</t>
-  </si>
-  <si>
-    <t>slider5</t>
-  </si>
-  <si>
     <t>theta_rel (0-1</t>
   </si>
   <si>
@@ -1016,6 +1001,9 @@
   </si>
   <si>
     <t>Wachstumsverlust durch Thripse</t>
+  </si>
+  <si>
+    <t>Hitzestress</t>
   </si>
 </sst>
 </file>
@@ -1487,15 +1475,15 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="s">
         <v>90</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1503,7 +1491,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1610,10 +1598,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1645,10 +1633,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1680,10 +1668,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1">
@@ -1715,10 +1703,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1">
@@ -1750,15 +1738,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B7" s="15">
         <v>45</v>
@@ -1770,13 +1758,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" t="s">
         <v>158</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>159</v>
-      </c>
-      <c r="G7" t="s">
-        <v>160</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -1785,15 +1773,15 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" s="15">
         <v>800000</v>
@@ -1805,13 +1793,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G8" t="s">
         <v>130</v>
-      </c>
-      <c r="F8" t="s">
-        <v>220</v>
-      </c>
-      <c r="G8" t="s">
-        <v>131</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -1820,15 +1808,15 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B9" s="15">
         <v>0.82</v>
@@ -1840,10 +1828,10 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -1852,15 +1840,15 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B10" s="15">
         <v>0.09</v>
@@ -1872,10 +1860,10 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>273</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>275</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -1884,10 +1872,10 @@
         <v>0.01</v>
       </c>
       <c r="J10" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1979,10 +1967,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2014,10 +2002,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2049,10 +2037,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2084,10 +2072,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2232,10 +2220,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2267,10 +2255,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2302,10 +2290,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2337,10 +2325,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2453,10 +2441,10 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -2465,10 +2453,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2488,10 +2476,10 @@
         <v>77</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2500,15 +2488,15 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B5">
         <v>0.3</v>
@@ -2521,7 +2509,7 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>82</v>
@@ -2533,10 +2521,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2554,10 +2542,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2566,10 +2554,10 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -2605,10 +2593,10 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2617,10 +2605,10 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -2640,10 +2628,10 @@
         <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2652,10 +2640,10 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -2673,10 +2661,10 @@
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -2685,15 +2673,15 @@
         <v>0.1</v>
       </c>
       <c r="J11" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -2706,10 +2694,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2718,10 +2706,10 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -2732,7 +2720,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="F14" s="9" t="s">
-        <v>89</v>
+        <v>320</v>
       </c>
       <c r="H14" t="s">
         <v>75</v>
@@ -2741,7 +2729,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" s="13">
         <v>30</v>
@@ -2756,10 +2744,10 @@
         <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2768,10 +2756,10 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -2779,7 +2767,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="14">
         <v>0.6</v>
@@ -2792,10 +2780,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -2804,10 +2792,10 @@
         <v>0.1</v>
       </c>
       <c r="J16" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -2815,7 +2803,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="14">
         <v>0.5</v>
@@ -2828,10 +2816,10 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2840,10 +2828,10 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -2851,7 +2839,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="14">
         <v>0.05</v>
@@ -2864,10 +2852,10 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2876,10 +2864,10 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -3051,7 +3039,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="F2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>75</v>
@@ -3059,7 +3047,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B3">
         <v>85</v>
@@ -3074,10 +3062,10 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -3086,15 +3074,15 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -3109,10 +3097,10 @@
         <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -3121,15 +3109,15 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3144,10 +3132,10 @@
         <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -3156,15 +3144,15 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6">
         <v>0.4</v>
@@ -3177,10 +3165,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -3189,15 +3177,15 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -3210,10 +3198,10 @@
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -3222,15 +3210,15 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8">
         <v>0.7</v>
@@ -3243,10 +3231,10 @@
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -3255,10 +3243,10 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3269,7 +3257,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="F10" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
         <v>75</v>
@@ -3278,7 +3266,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B11">
         <v>85</v>
@@ -3293,10 +3281,10 @@
         <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -3305,15 +3293,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -3328,10 +3316,10 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -3340,15 +3328,15 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -3363,10 +3351,10 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -3375,15 +3363,15 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -3398,10 +3386,10 @@
         <v>77</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -3410,15 +3398,15 @@
         <v>0.1</v>
       </c>
       <c r="J14" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15">
         <v>0.3</v>
@@ -3431,10 +3419,10 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -3443,15 +3431,15 @@
         <v>0.1</v>
       </c>
       <c r="J15" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16">
         <v>0.7</v>
@@ -3464,10 +3452,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3476,10 +3464,10 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3491,7 +3479,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="F18" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G18"/>
       <c r="H18" t="s">
@@ -3501,7 +3489,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -3516,10 +3504,10 @@
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -3528,15 +3516,15 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -3551,10 +3539,10 @@
         <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -3563,15 +3551,15 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -3586,10 +3574,10 @@
         <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -3598,15 +3586,15 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22">
         <v>0.1</v>
@@ -3621,10 +3609,10 @@
         <v>77</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H22" t="s">
         <v>19</v>
@@ -3633,15 +3621,15 @@
         <v>0.1</v>
       </c>
       <c r="J22" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23">
         <v>0.4</v>
@@ -3654,10 +3642,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G23" s="12" t="s">
         <v>245</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3666,15 +3654,15 @@
         <v>0.1</v>
       </c>
       <c r="J23" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24">
         <v>0.7</v>
@@ -3687,10 +3675,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3699,10 +3687,10 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3726,7 +3714,7 @@
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G26"/>
       <c r="H26" t="s">
@@ -3737,7 +3725,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B27">
         <v>40</v>
@@ -3749,13 +3737,13 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F27" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
@@ -3764,15 +3752,15 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28">
         <v>26</v>
@@ -3787,10 +3775,10 @@
         <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
@@ -3799,15 +3787,15 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -3822,10 +3810,10 @@
         <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -3834,15 +3822,15 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B30">
         <v>0.3</v>
@@ -3855,10 +3843,10 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -3867,15 +3855,15 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B31">
         <v>0.2</v>
@@ -3888,10 +3876,10 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
@@ -3900,15 +3888,15 @@
         <v>0.1</v>
       </c>
       <c r="J31" t="s">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B32">
         <v>0.8</v>
@@ -3921,10 +3909,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="G32" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -3933,10 +3921,10 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -4186,7 +4174,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2">
         <v>250</v>
@@ -4198,13 +4186,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" t="s">
         <v>112</v>
-      </c>
-      <c r="F2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" t="s">
-        <v>113</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4216,12 +4204,12 @@
         <v>76</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -4233,13 +4221,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -4251,12 +4239,12 @@
         <v>76</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B4">
         <v>1400</v>
@@ -4268,13 +4256,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -4286,12 +4274,12 @@
         <v>76</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B5">
         <v>1800</v>
@@ -4303,13 +4291,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -4321,12 +4309,12 @@
         <v>76</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B6" s="5">
         <v>10</v>
@@ -4338,13 +4326,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -4353,15 +4341,15 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B7" s="5">
         <v>180</v>
@@ -4373,13 +4361,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4388,15 +4376,15 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" s="5">
         <v>320</v>
@@ -4408,13 +4396,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4423,15 +4411,15 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" s="5">
         <v>220</v>
@@ -4443,13 +4431,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -4458,15 +4446,15 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10">
         <v>0.75</v>
@@ -4479,13 +4467,13 @@
       </c>
       <c r="E10"/>
       <c r="F10" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>123</v>
-      </c>
       <c r="H10" t="s">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="I10">
         <v>0.05</v>
@@ -4494,12 +4482,12 @@
         <v>76</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11">
         <v>19</v>
@@ -4514,10 +4502,10 @@
         <v>87</v>
       </c>
       <c r="F11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -4526,15 +4514,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -4549,10 +4537,10 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -4561,15 +4549,15 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13">
         <v>28</v>
@@ -4584,10 +4572,10 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G13" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -4596,15 +4584,15 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -4619,10 +4607,10 @@
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G14" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -4631,15 +4619,15 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B15">
         <v>0.9</v>
@@ -4651,30 +4639,30 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G15" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="J15" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B16">
         <v>0.55000000000000004</v>
@@ -4686,30 +4674,30 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F16" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B17">
         <v>0.25</v>
@@ -4721,30 +4709,30 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F17" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G17" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
       </c>
       <c r="I17">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J17" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B18">
         <v>0.6</v>
@@ -4756,13 +4744,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -4774,12 +4762,12 @@
         <v>76</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4791,16 +4779,16 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H19" t="s">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="I19">
         <v>0.1</v>
@@ -4809,12 +4797,12 @@
         <v>76</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B20">
         <v>4.5</v>
@@ -4826,16 +4814,16 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H20" t="s">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="I20">
         <v>0.1</v>
@@ -4844,12 +4832,12 @@
         <v>76</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B21">
         <v>3.5</v>
@@ -4861,16 +4849,16 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H21" t="s">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="I21">
         <v>0.1</v>
@@ -4879,7 +4867,7 @@
         <v>76</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4942,7 +4930,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B2">
         <v>0.16</v>
@@ -4954,13 +4942,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4969,15 +4957,15 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B3">
         <v>0.85</v>
@@ -4989,30 +4977,30 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G3" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="H3" t="s">
         <v>317</v>
-      </c>
-      <c r="H3" t="s">
-        <v>322</v>
       </c>
       <c r="I3">
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B4">
         <v>0.85</v>
@@ -5024,13 +5012,13 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -5039,15 +5027,15 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5">
         <v>0.25</v>
@@ -5059,13 +5047,13 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -5074,15 +5062,15 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -5094,13 +5082,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F6" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -5109,15 +5097,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B7">
         <v>12</v>
@@ -5129,13 +5117,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" t="s">
+        <v>305</v>
+      </c>
+      <c r="G7" t="s">
         <v>198</v>
-      </c>
-      <c r="F7" t="s">
-        <v>310</v>
-      </c>
-      <c r="G7" t="s">
-        <v>199</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -5144,15 +5132,15 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -5164,13 +5152,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="G8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -5179,15 +5167,15 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B9">
         <v>22</v>
@@ -5199,13 +5187,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F9" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="G9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -5214,15 +5202,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B10">
         <v>27</v>
@@ -5234,13 +5222,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F10" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="G10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -5249,15 +5237,15 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B11">
         <v>0.6</v>
@@ -5269,10 +5257,10 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
+        <v>206</v>
+      </c>
+      <c r="G11" t="s">
         <v>207</v>
-      </c>
-      <c r="G11" t="s">
-        <v>208</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -5284,12 +5272,12 @@
         <v>76</v>
       </c>
       <c r="K11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12">
         <v>0.9</v>
@@ -5301,10 +5289,10 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12" t="s">
         <v>210</v>
-      </c>
-      <c r="G12" t="s">
-        <v>211</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -5316,12 +5304,12 @@
         <v>76</v>
       </c>
       <c r="K12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -5333,10 +5321,10 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" t="s">
         <v>213</v>
-      </c>
-      <c r="G13" t="s">
-        <v>214</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -5348,12 +5336,12 @@
         <v>76</v>
       </c>
       <c r="K13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14">
         <v>0.75</v>
@@ -5365,10 +5353,10 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
+        <v>215</v>
+      </c>
+      <c r="G14" t="s">
         <v>216</v>
-      </c>
-      <c r="G14" t="s">
-        <v>217</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -5380,7 +5368,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5471,10 +5459,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L2"/>
       <c r="M2"/>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\GitHub\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0845C9F0-5B71-4C75-8C0F-8EC213108C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FC2B62-1925-4E39-BC22-D09F863A0E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="320">
   <si>
     <t>variable</t>
   </si>
@@ -736,9 +736,6 @@
     <t>Wachstumsverlust durch Zwiebelhalsfäule</t>
   </si>
   <si>
-    <t>Wachstumsverlust durch durch Starkregen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wachstumsverlust durchdurch Hagelereignis </t>
   </si>
   <si>
@@ -802,12 +799,6 @@
     <t>Ab dieser Regenmenge pro Tag besteht hohes Risiko für Schäden durch zu hohe Niederschläge</t>
   </si>
   <si>
-    <t>Tagesschwelle  Starkregen (mittleres Risiko) (Überschreitung = Risiko) [mm/Tag]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tagesschwelle Starkregen (hohes Risiko)(Überschreitung = Risiko) [mm/Tag]</t>
-  </si>
-  <si>
     <t>Niederschlagsschwelle für Hagelereignisse (Überschreitung = Risiko) [mm/Tag]</t>
   </si>
   <si>
@@ -964,9 +955,6 @@
     <t>effektive Wurzeltiefe (vegetative Phase) [cm]</t>
   </si>
   <si>
-    <t>effektive Wurzeltiefe (Bulbing-Phase) [cm]</t>
-  </si>
-  <si>
     <t>effektive Wurzeltiefe (Reifephase) [cm]</t>
   </si>
   <si>
@@ -994,9 +982,6 @@
     <t>fc_target_frac_t</t>
   </si>
   <si>
-    <t>silder2</t>
-  </si>
-  <si>
     <t>Wie viel Prozent des Wachstums geht bei Thripsbefall verloren? (z.B. 0.5 = 50% weniger Wachstum durch Saugschäden, Versilberungen und Nekrosen am Laub)</t>
   </si>
   <si>
@@ -1004,6 +989,18 @@
   </si>
   <si>
     <t>Hitzestress</t>
+  </si>
+  <si>
+    <t>Tagesschwelle  Starkregenschaden (mittleres Risiko) (Überschreitung = Risiko) [mm/Tag]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tagesschwelle Starkregenschaden (hohes Risiko)(Überschreitung = Risiko) [mm/Tag]</t>
+  </si>
+  <si>
+    <t>Wachstumsverlust durch durch Starkregenschaden</t>
+  </si>
+  <si>
+    <t>effektive Wurzeltiefe (Bulbenbildungs-Phase) [cm]</t>
   </si>
 </sst>
 </file>
@@ -1598,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K2" t="s">
         <v>148</v>
@@ -1633,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K3" t="s">
         <v>148</v>
@@ -1668,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K4" t="s">
         <v>148</v>
@@ -1703,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K5" t="s">
         <v>148</v>
@@ -1738,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K6" t="s">
         <v>148</v>
@@ -1773,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K7" t="s">
         <v>149</v>
@@ -1808,7 +1805,7 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K8" t="s">
         <v>149</v>
@@ -1831,7 +1828,7 @@
         <v>127</v>
       </c>
       <c r="G9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -1840,7 +1837,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K9" t="s">
         <v>149</v>
@@ -1848,7 +1845,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B10" s="15">
         <v>0.09</v>
@@ -1860,10 +1857,10 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -1872,7 +1869,7 @@
         <v>0.01</v>
       </c>
       <c r="J10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K10" t="s">
         <v>149</v>
@@ -1967,7 +1964,7 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K2" t="s">
         <v>148</v>
@@ -2002,7 +1999,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K3" t="s">
         <v>148</v>
@@ -2037,7 +2034,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K4" t="s">
         <v>148</v>
@@ -2072,7 +2069,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K5" t="s">
         <v>148</v>
@@ -2220,7 +2217,7 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K2" t="s">
         <v>148</v>
@@ -2255,7 +2252,7 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K3" t="s">
         <v>148</v>
@@ -2290,7 +2287,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K4" t="s">
         <v>148</v>
@@ -2325,7 +2322,7 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K5" t="s">
         <v>148</v>
@@ -2441,7 +2438,7 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>316</v>
       </c>
       <c r="G3" t="s">
         <v>222</v>
@@ -2453,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K3" t="s">
         <v>149</v>
@@ -2476,10 +2473,10 @@
         <v>77</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>254</v>
+        <v>317</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2488,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K4" t="s">
         <v>149</v>
@@ -2542,7 +2539,7 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>231</v>
+        <v>318</v>
       </c>
       <c r="G6" t="s">
         <v>226</v>
@@ -2554,7 +2551,7 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K6" t="s">
         <v>149</v>
@@ -2593,7 +2590,7 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G9" t="s">
         <v>179</v>
@@ -2605,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K9" t="s">
         <v>149</v>
@@ -2640,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K10" t="s">
         <v>149</v>
@@ -2694,7 +2691,7 @@
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" t="s">
         <v>225</v>
@@ -2706,7 +2703,7 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K12" t="s">
         <v>149</v>
@@ -2720,7 +2717,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="F14" s="9" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H14" t="s">
         <v>75</v>
@@ -2744,7 +2741,7 @@
         <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G15" t="s">
         <v>220</v>
@@ -2756,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K15" t="s">
         <v>149</v>
@@ -2852,7 +2849,7 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G18" t="s">
         <v>224</v>
@@ -2864,7 +2861,7 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K18" t="s">
         <v>149</v>
@@ -3062,7 +3059,7 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G3" t="s">
         <v>227</v>
@@ -3074,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>149</v>
@@ -3109,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>149</v>
@@ -3132,7 +3129,7 @@
         <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G5" t="s">
         <v>165</v>
@@ -3144,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>149</v>
@@ -3243,7 +3240,7 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>149</v>
@@ -3281,7 +3278,7 @@
         <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G11" t="s">
         <v>168</v>
@@ -3293,7 +3290,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>149</v>
@@ -3316,7 +3313,7 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G12" t="s">
         <v>169</v>
@@ -3328,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>149</v>
@@ -3351,7 +3348,7 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G13" t="s">
         <v>170</v>
@@ -3363,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>149</v>
@@ -3386,7 +3383,7 @@
         <v>77</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>166</v>
@@ -3419,7 +3416,7 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>166</v>
@@ -3452,10 +3449,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
+        <v>236</v>
+      </c>
+      <c r="G16" t="s">
         <v>237</v>
-      </c>
-      <c r="G16" t="s">
-        <v>238</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3464,7 +3461,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>149</v>
@@ -3504,7 +3501,7 @@
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G19" t="s">
         <v>171</v>
@@ -3516,7 +3513,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>149</v>
@@ -3539,7 +3536,7 @@
         <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G20" t="s">
         <v>172</v>
@@ -3551,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>149</v>
@@ -3574,7 +3571,7 @@
         <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G21" t="s">
         <v>173</v>
@@ -3586,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>149</v>
@@ -3609,7 +3606,7 @@
         <v>77</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>166</v>
@@ -3642,10 +3639,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3675,10 +3672,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
+        <v>245</v>
+      </c>
+      <c r="G24" t="s">
         <v>246</v>
-      </c>
-      <c r="G24" t="s">
-        <v>247</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3687,7 +3684,7 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>149</v>
@@ -3740,7 +3737,7 @@
         <v>221</v>
       </c>
       <c r="F27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G27" t="s">
         <v>174</v>
@@ -3752,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>149</v>
@@ -3775,7 +3772,7 @@
         <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G28" t="s">
         <v>175</v>
@@ -3787,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>149</v>
@@ -3810,7 +3807,7 @@
         <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G29" t="s">
         <v>176</v>
@@ -3822,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>149</v>
@@ -3843,7 +3840,7 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>166</v>
@@ -3876,7 +3873,7 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>177</v>
@@ -3909,10 +3906,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G32" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -3921,7 +3918,7 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>149</v>
@@ -4189,7 +4186,7 @@
         <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G2" t="s">
         <v>112</v>
@@ -4224,7 +4221,7 @@
         <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G3" t="s">
         <v>114</v>
@@ -4259,7 +4256,7 @@
         <v>111</v>
       </c>
       <c r="F4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G4" t="s">
         <v>116</v>
@@ -4294,7 +4291,7 @@
         <v>111</v>
       </c>
       <c r="F5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G5" t="s">
         <v>118</v>
@@ -4341,7 +4338,7 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>149</v>
@@ -4376,7 +4373,7 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>149</v>
@@ -4399,7 +4396,7 @@
         <v>189</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G8" t="s">
         <v>162</v>
@@ -4411,7 +4408,7 @@
         <v>0.1</v>
       </c>
       <c r="J8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>149</v>
@@ -4434,7 +4431,7 @@
         <v>189</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G9" t="s">
         <v>163</v>
@@ -4446,7 +4443,7 @@
         <v>0.1</v>
       </c>
       <c r="J9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>149</v>
@@ -4502,10 +4499,10 @@
         <v>87</v>
       </c>
       <c r="F11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -4514,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>149</v>
@@ -4537,10 +4534,10 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -4549,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>149</v>
@@ -4572,10 +4569,10 @@
         <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G13" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -4584,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>149</v>
@@ -4607,10 +4604,10 @@
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -4619,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>149</v>
@@ -4627,7 +4624,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B15">
         <v>0.9</v>
@@ -4639,13 +4636,13 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F15" t="s">
         <v>284</v>
       </c>
-      <c r="F15" t="s">
-        <v>287</v>
-      </c>
       <c r="G15" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -4654,7 +4651,7 @@
         <v>0.05</v>
       </c>
       <c r="J15" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>149</v>
@@ -4662,7 +4659,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B16">
         <v>0.55000000000000004</v>
@@ -4674,13 +4671,13 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" t="s">
         <v>285</v>
       </c>
-      <c r="F16" t="s">
-        <v>288</v>
-      </c>
       <c r="G16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -4689,7 +4686,7 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>149</v>
@@ -4697,7 +4694,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B17">
         <v>0.25</v>
@@ -4709,13 +4706,13 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
+        <v>283</v>
+      </c>
+      <c r="F17" t="s">
         <v>286</v>
       </c>
-      <c r="F17" t="s">
-        <v>289</v>
-      </c>
       <c r="G17" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -4724,7 +4721,7 @@
         <v>0.05</v>
       </c>
       <c r="J17" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>149</v>
@@ -4732,7 +4729,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B18">
         <v>0.6</v>
@@ -4747,10 +4744,10 @@
         <v>119</v>
       </c>
       <c r="F18" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G18" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -4767,7 +4764,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4782,10 +4779,10 @@
         <v>119</v>
       </c>
       <c r="F19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G19" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -4802,7 +4799,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B20">
         <v>4.5</v>
@@ -4817,10 +4814,10 @@
         <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G20" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -4837,7 +4834,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B21">
         <v>3.5</v>
@@ -4852,10 +4849,10 @@
         <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G21" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -4945,10 +4942,10 @@
         <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4957,7 +4954,7 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K2" t="s">
         <v>149</v>
@@ -4965,7 +4962,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B3">
         <v>0.85</v>
@@ -4980,19 +4977,19 @@
         <v>192</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H3" t="s">
-        <v>317</v>
+        <v>19</v>
       </c>
       <c r="I3">
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K3" t="s">
         <v>149</v>
@@ -5000,7 +4997,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B4">
         <v>0.85</v>
@@ -5015,10 +5012,10 @@
         <v>192</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -5027,7 +5024,7 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K4" t="s">
         <v>149</v>
@@ -5050,10 +5047,10 @@
         <v>192</v>
       </c>
       <c r="F5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -5062,7 +5059,7 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K5" t="s">
         <v>149</v>
@@ -5085,10 +5082,10 @@
         <v>195</v>
       </c>
       <c r="F6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -5097,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K6" t="s">
         <v>149</v>
@@ -5120,7 +5117,7 @@
         <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G7" t="s">
         <v>198</v>
@@ -5132,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K7" t="s">
         <v>149</v>
@@ -5155,7 +5152,7 @@
         <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G8" t="s">
         <v>200</v>
@@ -5167,7 +5164,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K8" t="s">
         <v>149</v>
@@ -5190,7 +5187,7 @@
         <v>197</v>
       </c>
       <c r="F9" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="G9" t="s">
         <v>202</v>
@@ -5202,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K9" t="s">
         <v>149</v>
@@ -5225,7 +5222,7 @@
         <v>197</v>
       </c>
       <c r="F10" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G10" t="s">
         <v>204</v>
@@ -5237,7 +5234,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K10" t="s">
         <v>149</v>
@@ -5459,7 +5456,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K2" t="s">
         <v>147</v>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\GitHub\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FC2B62-1925-4E39-BC22-D09F863A0E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1260ADB-F87C-44E9-9C7D-6300574837D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -1802,7 +1802,7 @@
         <v>19</v>
       </c>
       <c r="I8">
-        <v>0.1</v>
+        <v>50000</v>
       </c>
       <c r="J8" t="s">
         <v>309</v>
@@ -1834,7 +1834,7 @@
         <v>19</v>
       </c>
       <c r="I9">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J9" t="s">
         <v>309</v>
@@ -4195,7 +4195,7 @@
         <v>19</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J2" t="s">
         <v>76</v>
@@ -4230,7 +4230,7 @@
         <v>19</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J3" t="s">
         <v>76</v>
@@ -4265,7 +4265,7 @@
         <v>19</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
         <v>76</v>
@@ -4300,7 +4300,7 @@
         <v>19</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J5" t="s">
         <v>76</v>
@@ -4335,7 +4335,7 @@
         <v>19</v>
       </c>
       <c r="I6">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
         <v>309</v>
@@ -4370,7 +4370,7 @@
         <v>19</v>
       </c>
       <c r="I7">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
         <v>309</v>
@@ -4405,7 +4405,7 @@
         <v>19</v>
       </c>
       <c r="I8">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
         <v>309</v>
@@ -4440,7 +4440,7 @@
         <v>19</v>
       </c>
       <c r="I9">
-        <v>0.1</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
         <v>309</v>

--- a/data/ASP_input_parameters_german2.xlsx
+++ b/data/ASP_input_parameters_german2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pauld\Documents\GitHub\Climate_Impact_on_Crop_Yield\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbsl\Documents\R-Projects\Climate_Impact_on_Crop_Yield\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1260ADB-F87C-44E9-9C7D-6300574837D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8D0FAB-FAA0-4763-9C17-20AE5D421262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="815" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="Sheet5" sheetId="17" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="11" r:id="rId7"/>
     <sheet name="Sheet7" sheetId="18" r:id="rId8"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId9"/>
+    <sheet name="Sheet8" sheetId="19" r:id="rId9"/>
+    <sheet name="Sheet9" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="364">
   <si>
     <t>variable</t>
   </si>
@@ -214,15 +215,9 @@
     <t>Hitze Schäden</t>
   </si>
   <si>
-    <t>Mögliche Schäden durch Spätfrost</t>
-  </si>
-  <si>
     <t>Mögliche Schäden durch Temperaturschwankungen</t>
   </si>
   <si>
-    <t>Mögliche Schäden durch Ernteversögerungen wegen Starkregen</t>
-  </si>
-  <si>
     <t>Mögliche Schäden durch Ernteverzägerungen bei Hitzewellen</t>
   </si>
   <si>
@@ -484,9 +479,6 @@
     <t>yield_reduction_hail_t</t>
   </si>
   <si>
-    <t>Spargel;Zwiebel</t>
-  </si>
-  <si>
     <t>Spargel</t>
   </si>
   <si>
@@ -1001,6 +993,147 @@
   </si>
   <si>
     <t>effektive Wurzeltiefe (Bulbenbildungs-Phase) [cm]</t>
+  </si>
+  <si>
+    <t>Spargel;Zwiebel;Erdbeere</t>
+  </si>
+  <si>
+    <t>Spargel;Erdbeere</t>
+  </si>
+  <si>
+    <t>Mögliche Schäden durch Ernteverzögerungen wegen Starkregen</t>
+  </si>
+  <si>
+    <t>Mögliche Schäden durch Spätfrost während der Ernte</t>
+  </si>
+  <si>
+    <t>harvest_fly_damage_t</t>
+  </si>
+  <si>
+    <t>Kirschessigfliege</t>
+  </si>
+  <si>
+    <t>Mögliche Schäden durch befall von Kirschessigfliege</t>
+  </si>
+  <si>
+    <t>Erdbeere</t>
+  </si>
+  <si>
+    <t>Hagelschaden</t>
+  </si>
+  <si>
+    <t>Mögliche Schäden durch Hagel während der Erntezeit</t>
+  </si>
+  <si>
+    <t>Schäden während Frühling</t>
+  </si>
+  <si>
+    <t>Blütenschäden durch Krankheiten</t>
+  </si>
+  <si>
+    <t>Blütenschäden durch Spätforst</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Trockenheit</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Spätfrost</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Hagel</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Sonnenbrand</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Insektenbefall</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Krankheiten</t>
+  </si>
+  <si>
+    <t>Fruchtschäden durch Schnecken</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Insektenbefall während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Krankheiten während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Schnecken während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Sonnenbrand während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Hagelschlag während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Trockenheit während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Fruchtschäden durch Spätfrost während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>Mögliche Blüteschäden durch Spätfrost im Frühling</t>
+  </si>
+  <si>
+    <t>Mögliche Blüteschäden durch Krankheiten im Frühling</t>
+  </si>
+  <si>
+    <t>spring_disease_dmg_t</t>
+  </si>
+  <si>
+    <t>spring_frost_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_frost_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_drought_stress_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_hail_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_sunburn_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_insect_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_disease_dmg_t</t>
+  </si>
+  <si>
+    <t>fruit_snail_dmg_t</t>
+  </si>
+  <si>
+    <t>T_opt_fruit_p</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>Durchschnittstemperatur Fruchtreife</t>
+  </si>
+  <si>
+    <t>Optimale Durchschnittstemperatur während der Fruchtreife</t>
+  </si>
+  <si>
+    <t>harvest_hail_damage_t</t>
+  </si>
+  <si>
+    <t>strawb_chill_need_p</t>
+  </si>
+  <si>
+    <t>strawb_photosynthetic_active_days_needed_p</t>
+  </si>
+  <si>
+    <t>strawb_expected_yield_p</t>
+  </si>
+  <si>
+    <t>t/ha</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1584,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1464,23 +1597,23 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -1488,7 +1621,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1496,9 +1629,17 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1512,6 +1653,202 @@
     <row r="19" spans="1:2">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E46615A-8238-4E62-BD61-353FBA21321A}">
+  <dimension ref="A1:N54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="21" style="1" customWidth="1"/>
+    <col min="7" max="7" width="52" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="106.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="F28" s="3"/>
+    </row>
+    <row r="36" spans="6:6">
+      <c r="F36" s="3"/>
+    </row>
+    <row r="42" spans="6:6">
+      <c r="F42" s="3"/>
+    </row>
+    <row r="49" spans="6:6">
+      <c r="F49" s="3"/>
+    </row>
+    <row r="54" spans="6:6">
+      <c r="F54" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1520,7 +1857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92018703-4177-49D8-B09E-62560F009CDF}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
@@ -1563,7 +1900,7 @@
         <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1595,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1630,10 +1967,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1665,10 +2002,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1">
@@ -1700,10 +2037,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1">
@@ -1735,15 +2072,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" s="15">
         <v>45</v>
@@ -1755,13 +2092,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -1770,15 +2107,15 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B8" s="15">
         <v>800000</v>
@@ -1790,13 +2127,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -1805,15 +2142,15 @@
         <v>50000</v>
       </c>
       <c r="J8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B9" s="15">
         <v>0.82</v>
@@ -1825,10 +2162,10 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -1837,15 +2174,15 @@
         <v>0.05</v>
       </c>
       <c r="J9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B10" s="15">
         <v>0.09</v>
@@ -1857,10 +2194,10 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -1869,10 +2206,150 @@
         <v>0.01</v>
       </c>
       <c r="J10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K10" t="s">
-        <v>149</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>355</v>
+      </c>
+      <c r="B11" s="15">
+        <v>13</v>
+      </c>
+      <c r="C11" s="15">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F11" t="s">
+        <v>357</v>
+      </c>
+      <c r="G11" t="s">
+        <v>358</v>
+      </c>
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>0.5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>306</v>
+      </c>
+      <c r="K11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B12" s="15">
+        <v>24</v>
+      </c>
+      <c r="C12" s="15">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>306</v>
+      </c>
+      <c r="K12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="1" customFormat="1">
+      <c r="A13" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B13" s="16">
+        <v>20</v>
+      </c>
+      <c r="C13" s="16">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>306</v>
+      </c>
+      <c r="K13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="1" customFormat="1">
+      <c r="A14" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B14" s="16">
+        <v>40</v>
+      </c>
+      <c r="C14" s="16">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>306</v>
+      </c>
+      <c r="K14" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -1932,7 +2409,7 @@
         <v>18</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1955,7 +2432,7 @@
         <v>53</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>57</v>
+        <v>320</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -1964,10 +2441,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
-        <v>148</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1990,7 +2467,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -1999,10 +2476,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2025,7 +2502,7 @@
         <v>55</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>59</v>
+        <v>319</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2034,10 +2511,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2060,7 +2537,7 @@
         <v>56</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -2069,17 +2546,81 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="J6"/>
+      <c r="A6" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>306</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="J7"/>
+      <c r="A7" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B7" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>306</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
       <c r="J8"/>
@@ -2185,7 +2726,7 @@
         <v>18</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2205,10 +2746,10 @@
         <v>38</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -2217,10 +2758,10 @@
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
-        <v>148</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2240,10 +2781,10 @@
         <v>38</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -2252,10 +2793,10 @@
         <v>0.1</v>
       </c>
       <c r="J3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
-        <v>148</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2275,10 +2816,10 @@
         <v>38</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2287,10 +2828,10 @@
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
-        <v>148</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2310,10 +2851,10 @@
         <v>38</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -2322,10 +2863,10 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2409,21 +2950,21 @@
         <v>18</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="F2" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K2"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>25</v>
@@ -2435,13 +2976,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -2450,15 +2991,15 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>45</v>
@@ -2470,13 +3011,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2485,15 +3026,15 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B5">
         <v>0.3</v>
@@ -2506,10 +3047,10 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -2518,15 +3059,15 @@
         <v>0.1</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>0.7</v>
@@ -2539,10 +3080,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2551,31 +3092,31 @@
         <v>0.05</v>
       </c>
       <c r="J6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="H7" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
     </row>
     <row r="8" spans="1:14">
       <c r="F8" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K8"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9">
         <v>20</v>
@@ -2587,13 +3128,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -2602,15 +3143,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>18</v>
@@ -2622,13 +3163,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2637,15 +3178,15 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2658,10 +3199,10 @@
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -2670,15 +3211,15 @@
         <v>0.1</v>
       </c>
       <c r="J11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -2691,10 +3232,10 @@
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2703,30 +3244,30 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="H13" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14">
       <c r="F14" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B15" s="13">
         <v>30</v>
@@ -2738,13 +3279,13 @@
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G15" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -2753,10 +3294,10 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -2764,7 +3305,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B16" s="14">
         <v>0.6</v>
@@ -2777,10 +3318,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" s="12" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -2789,10 +3330,10 @@
         <v>0.1</v>
       </c>
       <c r="J16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -2800,7 +3341,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B17" s="14">
         <v>0.5</v>
@@ -2813,10 +3354,10 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2825,10 +3366,10 @@
         <v>0.1</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -2836,7 +3377,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B18" s="14">
         <v>0.05</v>
@@ -2849,10 +3390,10 @@
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2861,10 +3402,10 @@
         <v>0.05</v>
       </c>
       <c r="J18" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -3029,22 +3570,22 @@
         <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B3">
         <v>85</v>
@@ -3056,13 +3597,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -3071,15 +3612,15 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -3091,13 +3632,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -3106,15 +3647,15 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3126,13 +3667,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -3141,15 +3682,15 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B6">
         <v>0.4</v>
@@ -3162,10 +3703,10 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -3174,15 +3715,15 @@
         <v>0.1</v>
       </c>
       <c r="J6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B7">
         <v>0.5</v>
@@ -3195,10 +3736,10 @@
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -3207,15 +3748,15 @@
         <v>0.1</v>
       </c>
       <c r="J7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B8">
         <v>0.7</v>
@@ -3228,10 +3769,10 @@
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -3240,30 +3781,30 @@
         <v>0.05</v>
       </c>
       <c r="J8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="H9" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:11">
       <c r="F10" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B11">
         <v>85</v>
@@ -3275,13 +3816,13 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -3290,15 +3831,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -3310,13 +3851,13 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G12" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -3325,15 +3866,15 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -3345,13 +3886,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -3360,15 +3901,15 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B14">
         <v>0.4</v>
@@ -3380,13 +3921,13 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -3395,15 +3936,15 @@
         <v>0.1</v>
       </c>
       <c r="J14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B15">
         <v>0.3</v>
@@ -3416,10 +3957,10 @@
       </c>
       <c r="E15"/>
       <c r="F15" s="12" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -3428,15 +3969,15 @@
         <v>0.1</v>
       </c>
       <c r="J15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B16">
         <v>0.7</v>
@@ -3449,10 +3990,10 @@
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3461,32 +4002,32 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="G17"/>
       <c r="H17" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J17"/>
     </row>
     <row r="18" spans="1:11">
       <c r="F18" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G18"/>
       <c r="H18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J18"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>80</v>
@@ -3498,13 +4039,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -3513,15 +4054,15 @@
         <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -3533,13 +4074,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -3548,15 +4089,15 @@
         <v>1</v>
       </c>
       <c r="J20" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -3568,13 +4109,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -3583,15 +4124,15 @@
         <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B22">
         <v>0.1</v>
@@ -3603,13 +4144,13 @@
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H22" t="s">
         <v>19</v>
@@ -3618,15 +4159,15 @@
         <v>0.1</v>
       </c>
       <c r="J22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B23">
         <v>0.4</v>
@@ -3639,10 +4180,10 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H23" t="s">
         <v>19</v>
@@ -3651,15 +4192,15 @@
         <v>0.1</v>
       </c>
       <c r="J23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B24">
         <v>0.7</v>
@@ -3672,10 +4213,10 @@
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G24" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H24" t="s">
         <v>19</v>
@@ -3684,10 +4225,10 @@
         <v>0.05</v>
       </c>
       <c r="J24" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3699,7 +4240,7 @@
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -3711,18 +4252,18 @@
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G26"/>
       <c r="H26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B27">
         <v>40</v>
@@ -3734,13 +4275,13 @@
         <v>5</v>
       </c>
       <c r="E27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F27" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
         <v>19</v>
@@ -3749,15 +4290,15 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28">
         <v>26</v>
@@ -3769,13 +4310,13 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G28" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H28" t="s">
         <v>19</v>
@@ -3784,15 +4325,15 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -3804,13 +4345,13 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G29" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -3819,15 +4360,15 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B30">
         <v>0.3</v>
@@ -3840,10 +4381,10 @@
       </c>
       <c r="E30"/>
       <c r="F30" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -3852,15 +4393,15 @@
         <v>0.1</v>
       </c>
       <c r="J30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B31">
         <v>0.2</v>
@@ -3873,10 +4414,10 @@
       </c>
       <c r="E31"/>
       <c r="F31" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
@@ -3885,15 +4426,15 @@
         <v>0.1</v>
       </c>
       <c r="J31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B32">
         <v>0.8</v>
@@ -3906,10 +4447,10 @@
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G32" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -3918,10 +4459,10 @@
         <v>0.05</v>
       </c>
       <c r="J32" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -4166,12 +4707,12 @@
         <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B2">
         <v>250</v>
@@ -4183,13 +4724,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4198,15 +4739,15 @@
         <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B3">
         <v>1000</v>
@@ -4218,13 +4759,13 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -4233,15 +4774,15 @@
         <v>50</v>
       </c>
       <c r="J3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B4">
         <v>1400</v>
@@ -4253,13 +4794,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -4268,15 +4809,15 @@
         <v>50</v>
       </c>
       <c r="J4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B5">
         <v>1800</v>
@@ -4288,13 +4829,13 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -4303,15 +4844,15 @@
         <v>50</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B6" s="5">
         <v>10</v>
@@ -4323,13 +4864,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -4338,15 +4879,15 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B7" s="5">
         <v>180</v>
@@ -4358,13 +4899,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -4373,15 +4914,15 @@
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B8" s="5">
         <v>320</v>
@@ -4393,13 +4934,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -4408,15 +4949,15 @@
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B9" s="5">
         <v>220</v>
@@ -4428,13 +4969,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -4443,15 +4984,15 @@
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B10">
         <v>0.75</v>
@@ -4464,10 +5005,10 @@
       </c>
       <c r="E10"/>
       <c r="F10" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -4476,15 +5017,15 @@
         <v>0.05</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>19</v>
@@ -4496,13 +5037,13 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -4511,15 +5052,15 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -4531,13 +5072,13 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -4546,15 +5087,15 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B13">
         <v>28</v>
@@ -4566,13 +5107,13 @@
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G13" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -4581,15 +5122,15 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -4601,13 +5142,13 @@
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -4616,15 +5157,15 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B15">
         <v>0.9</v>
@@ -4636,13 +5177,13 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
+        <v>278</v>
+      </c>
+      <c r="F15" t="s">
         <v>281</v>
       </c>
-      <c r="F15" t="s">
-        <v>284</v>
-      </c>
       <c r="G15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H15" t="s">
         <v>19</v>
@@ -4651,15 +5192,15 @@
         <v>0.05</v>
       </c>
       <c r="J15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B16">
         <v>0.55000000000000004</v>
@@ -4671,13 +5212,13 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
+        <v>279</v>
+      </c>
+      <c r="F16" t="s">
         <v>282</v>
       </c>
-      <c r="F16" t="s">
-        <v>285</v>
-      </c>
       <c r="G16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -4686,15 +5227,15 @@
         <v>0.05</v>
       </c>
       <c r="J16" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B17">
         <v>0.25</v>
@@ -4706,13 +5247,13 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
+        <v>280</v>
+      </c>
+      <c r="F17" t="s">
         <v>283</v>
       </c>
-      <c r="F17" t="s">
-        <v>286</v>
-      </c>
       <c r="G17" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -4721,15 +5262,15 @@
         <v>0.05</v>
       </c>
       <c r="J17" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B18">
         <v>0.6</v>
@@ -4741,13 +5282,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -4756,15 +5297,15 @@
         <v>0.1</v>
       </c>
       <c r="J18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -4776,13 +5317,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -4791,15 +5332,15 @@
         <v>0.1</v>
       </c>
       <c r="J19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B20">
         <v>4.5</v>
@@ -4811,13 +5352,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -4826,15 +5367,15 @@
         <v>0.1</v>
       </c>
       <c r="J20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B21">
         <v>3.5</v>
@@ -4846,13 +5387,13 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -4861,10 +5402,10 @@
         <v>0.1</v>
       </c>
       <c r="J21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4922,12 +5463,12 @@
         <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B2">
         <v>0.16</v>
@@ -4939,13 +5480,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
         <v>19</v>
@@ -4954,15 +5495,15 @@
         <v>0.01</v>
       </c>
       <c r="J2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B3">
         <v>0.85</v>
@@ -4974,13 +5515,13 @@
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -4989,15 +5530,15 @@
         <v>0.05</v>
       </c>
       <c r="J3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B4">
         <v>0.85</v>
@@ -5009,13 +5550,13 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -5024,15 +5565,15 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B5">
         <v>0.25</v>
@@ -5044,13 +5585,13 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -5059,15 +5600,15 @@
         <v>0.05</v>
       </c>
       <c r="J5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -5079,13 +5620,13 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -5094,15 +5635,15 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B7">
         <v>12</v>
@@ -5114,13 +5655,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -5129,15 +5670,15 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -5149,13 +5690,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" t="s">
+        <v>300</v>
+      </c>
+      <c r="G8" t="s">
         <v>197</v>
-      </c>
-      <c r="F8" t="s">
-        <v>303</v>
-      </c>
-      <c r="G8" t="s">
-        <v>200</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -5164,15 +5705,15 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B9">
         <v>22</v>
@@ -5184,13 +5725,13 @@
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H9" t="s">
         <v>19</v>
@@ -5199,15 +5740,15 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B10">
         <v>27</v>
@@ -5219,13 +5760,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -5234,15 +5775,15 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B11">
         <v>0.6</v>
@@ -5254,10 +5795,10 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -5266,15 +5807,15 @@
         <v>0.05</v>
       </c>
       <c r="J11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>0.9</v>
@@ -5286,10 +5827,10 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -5298,15 +5839,15 @@
         <v>0.05</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -5318,10 +5859,10 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H13" t="s">
         <v>19</v>
@@ -5330,15 +5871,15 @@
         <v>0.05</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B14">
         <v>0.75</v>
@@ -5350,10 +5891,10 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H14" t="s">
         <v>19</v>
@@ -5362,10 +5903,10 @@
         <v>0.05</v>
       </c>
       <c r="J14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -5376,23 +5917,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E46615A-8238-4E62-BD61-353FBA21321A}">
-  <dimension ref="A1:N54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561F91AF-F78C-4DD0-B44C-BA36A0F9F918}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="21" style="1" customWidth="1"/>
-    <col min="7" max="7" width="52" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="106.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="42.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5424,149 +5958,339 @@
         <v>18</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="7">
-        <v>1000</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" t="s">
         <v>70</v>
       </c>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:14" ht="15.75">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.75">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="F28" s="3"/>
-    </row>
-    <row r="36" spans="6:6">
-      <c r="F36" s="3"/>
-    </row>
-    <row r="42" spans="6:6">
-      <c r="F42" s="3"/>
-    </row>
-    <row r="49" spans="6:6">
-      <c r="F49" s="3"/>
-    </row>
-    <row r="54" spans="6:6">
-      <c r="F54" s="3"/>
+        <v>324</v>
+      </c>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3">
+        <v>0.1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K3" t="s">
+        <v>324</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>306</v>
+      </c>
+      <c r="K4" t="s">
+        <v>324</v>
+      </c>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>0.1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>306</v>
+      </c>
+      <c r="K5" t="s">
+        <v>324</v>
+      </c>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>0.1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>306</v>
+      </c>
+      <c r="K6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7">
+        <v>0.1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>306</v>
+      </c>
+      <c r="K7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B8" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>306</v>
+      </c>
+      <c r="K8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B9" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>306</v>
+      </c>
+      <c r="K9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B10" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <v>0.1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>306</v>
+      </c>
+      <c r="K10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="F13" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>